--- a/exports/historical-tariffs-ready.xlsx
+++ b/exports/historical-tariffs-ready.xlsx
@@ -6,7 +6,8 @@
     <sheet name="Tarifas finales" sheetId="1" r:id="rId1"/>
     <sheet name="Importes especiales" sheetId="2" r:id="rId2"/>
     <sheet name="Alertas" sheetId="3" r:id="rId3"/>
-    <sheet name="Resumen" sheetId="4" r:id="rId4"/>
+    <sheet name="Solapamientos" sheetId="4" r:id="rId4"/>
+    <sheet name="Resumen" sheetId="5" r:id="rId5"/>
   </sheets>
 </workbook>
 </file>
@@ -400,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H87"/>
+  <dimension ref="A1:H74"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -471,7 +472,7 @@
         <v>2025-03-01</v>
       </c>
       <c r="F3" t="str">
-        <v>2025-07-31</v>
+        <v>2025-08-31</v>
       </c>
       <c r="G3" t="str">
         <v>2025-03 = $20000.00</v>
@@ -488,19 +489,19 @@
         <v>Árabe infantil</v>
       </c>
       <c r="C4" t="str">
-        <v>Histórica - Árabe infantil - 2026 - $40.000</v>
+        <v>Histórica - Árabe infantil - 2025 - $30.000</v>
       </c>
       <c r="D4" t="str">
-        <v>40000.00</v>
+        <v>30000.00</v>
       </c>
       <c r="E4" t="str">
-        <v>2026-08-01</v>
+        <v>2025-09-01</v>
       </c>
       <c r="F4" t="str">
-        <v>2026-08-31</v>
+        <v>2025-11-30</v>
       </c>
       <c r="G4" t="str">
-        <v>2026-08 = $40000.00</v>
+        <v/>
       </c>
       <c r="H4" t="str">
         <v/>
@@ -508,25 +509,25 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>d06eb88b-a6e3-4cda-8bf9-5278455b3b7e</v>
+        <v>2b9ee038-bf48-4bb5-9315-c2015733d11c</v>
       </c>
       <c r="B5" t="str">
-        <v>Bachata en Pareja</v>
+        <v>Árabe infantil</v>
       </c>
       <c r="C5" t="str">
-        <v>Histórica - Bachata en Pareja - 2026 - $15.000</v>
+        <v>Histórica - Árabe infantil - 2026 - $30.000</v>
       </c>
       <c r="D5" t="str">
-        <v>15000.00</v>
+        <v>30000.00</v>
       </c>
       <c r="E5" t="str">
-        <v>2026-02-01</v>
+        <v>2026-01-01</v>
       </c>
       <c r="F5" t="str">
-        <v>2026-02-28</v>
+        <v>2026-07-31</v>
       </c>
       <c r="G5" t="str">
-        <v>2026-02 = $15000.00</v>
+        <v/>
       </c>
       <c r="H5" t="str">
         <v/>
@@ -534,25 +535,25 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>8da07d2d-b252-4618-9370-34f8ca23e93e</v>
+        <v>2b9ee038-bf48-4bb5-9315-c2015733d11c</v>
       </c>
       <c r="B6" t="str">
-        <v>Bachata Pasos Sueltos</v>
+        <v>Árabe infantil</v>
       </c>
       <c r="C6" t="str">
-        <v>Histórica - Bachata Pasos Sueltos - 2026 - $30.000</v>
+        <v>Histórica - Árabe infantil - 2026 - $40.000</v>
       </c>
       <c r="D6" t="str">
-        <v>30000.00</v>
+        <v>40000.00</v>
       </c>
       <c r="E6" t="str">
-        <v>2026-02-01</v>
+        <v>2026-08-01</v>
       </c>
       <c r="F6" t="str">
-        <v>2026-02-28</v>
+        <v>2026-08-31</v>
       </c>
       <c r="G6" t="str">
-        <v>2026-02 = $30000.00</v>
+        <v>2026-08 = $40000.00</v>
       </c>
       <c r="H6" t="str">
         <v/>
@@ -560,25 +561,25 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>acbbc26b-2a55-4952-97a0-92dc025024d2</v>
+        <v>d06eb88b-a6e3-4cda-8bf9-5278455b3b7e</v>
       </c>
       <c r="B7" t="str">
-        <v>Bachata y Salsa Inicial</v>
+        <v>Bachata en Pareja</v>
       </c>
       <c r="C7" t="str">
-        <v>Histórica - Bachata y Salsa Inicial - 2025 - $15.000</v>
+        <v>Histórica - Bachata en Pareja - 2026 - $15.000</v>
       </c>
       <c r="D7" t="str">
         <v>15000.00</v>
       </c>
       <c r="E7" t="str">
-        <v>2025-02-01</v>
+        <v>2026-02-01</v>
       </c>
       <c r="F7" t="str">
-        <v>2025-02-28</v>
+        <v>2026-02-28</v>
       </c>
       <c r="G7" t="str">
-        <v>2025-02 = $15000.00</v>
+        <v>2026-02 = $15000.00</v>
       </c>
       <c r="H7" t="str">
         <v/>
@@ -586,25 +587,25 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>acbbc26b-2a55-4952-97a0-92dc025024d2</v>
+        <v>8da07d2d-b252-4618-9370-34f8ca23e93e</v>
       </c>
       <c r="B8" t="str">
-        <v>Bachata y Salsa Inicial</v>
+        <v>Bachata Pasos Sueltos</v>
       </c>
       <c r="C8" t="str">
-        <v>Histórica - Bachata y Salsa Inicial - 2025 - $10.000</v>
+        <v>Histórica - Bachata Pasos Sueltos - 2026 - $30.000</v>
       </c>
       <c r="D8" t="str">
-        <v>10000.00</v>
+        <v>30000.00</v>
       </c>
       <c r="E8" t="str">
-        <v>2025-03-01</v>
+        <v>2026-02-01</v>
       </c>
       <c r="F8" t="str">
-        <v>2025-05-31</v>
+        <v>2026-02-28</v>
       </c>
       <c r="G8" t="str">
-        <v>2025-03 = $10000.00</v>
+        <v>2026-02 = $30000.00</v>
       </c>
       <c r="H8" t="str">
         <v/>
@@ -618,19 +619,19 @@
         <v>Bachata y Salsa Inicial</v>
       </c>
       <c r="C9" t="str">
-        <v>Histórica - Bachata y Salsa Inicial - 2025 - $20.000</v>
+        <v>Histórica - Bachata y Salsa Inicial - 2025 - $15.000</v>
       </c>
       <c r="D9" t="str">
-        <v>20000.00</v>
+        <v>15000.00</v>
       </c>
       <c r="E9" t="str">
-        <v>2025-06-01</v>
+        <v>2025-02-01</v>
       </c>
       <c r="F9" t="str">
-        <v>2025-07-31</v>
+        <v>2025-02-28</v>
       </c>
       <c r="G9" t="str">
-        <v>2025-06 = $20000.00</v>
+        <v>2025-02 = $15000.00</v>
       </c>
       <c r="H9" t="str">
         <v/>
@@ -644,19 +645,19 @@
         <v>Bachata y Salsa Inicial</v>
       </c>
       <c r="C10" t="str">
-        <v>Histórica - Bachata y Salsa Inicial - 2025 - $30.000</v>
+        <v>Histórica - Bachata y Salsa Inicial - 2025 - $10.000</v>
       </c>
       <c r="D10" t="str">
-        <v>30000.00</v>
+        <v>10000.00</v>
       </c>
       <c r="E10" t="str">
-        <v>2025-09-01</v>
+        <v>2025-03-01</v>
       </c>
       <c r="F10" t="str">
-        <v>2025-10-31</v>
+        <v>2025-05-31</v>
       </c>
       <c r="G10" t="str">
-        <v>2025-09 = $30000.00</v>
+        <v>2025-03 = $10000.00</v>
       </c>
       <c r="H10" t="str">
         <v/>
@@ -670,19 +671,19 @@
         <v>Bachata y Salsa Inicial</v>
       </c>
       <c r="C11" t="str">
-        <v>Histórica - Bachata y Salsa Inicial - 2025 - $25.000</v>
+        <v>Histórica - Bachata y Salsa Inicial - 2025 - $20.000</v>
       </c>
       <c r="D11" t="str">
-        <v>25000.00</v>
+        <v>20000.00</v>
       </c>
       <c r="E11" t="str">
-        <v>2025-10-01</v>
+        <v>2025-06-01</v>
       </c>
       <c r="F11" t="str">
-        <v>2025-10-31</v>
+        <v>2025-08-31</v>
       </c>
       <c r="G11" t="str">
-        <v>2025-10 = $25000.00</v>
+        <v>2025-06 = $20000.00</v>
       </c>
       <c r="H11" t="str">
         <v/>
@@ -696,22 +697,22 @@
         <v>Bachata y Salsa Inicial</v>
       </c>
       <c r="C12" t="str">
-        <v>Histórica - Bachata y Salsa Inicial - 2026 - $30.000</v>
+        <v>Histórica - Bachata y Salsa Inicial - 2025 - $30.000</v>
       </c>
       <c r="D12" t="str">
         <v>30000.00</v>
       </c>
       <c r="E12" t="str">
-        <v>2026-05-01</v>
+        <v>2025-09-01</v>
       </c>
       <c r="F12" t="str">
-        <v>2026-07-31</v>
+        <v>2025-11-30</v>
       </c>
       <c r="G12" t="str">
-        <v>2026-05 = $30000.00</v>
+        <v>2025-09 = $30000.00</v>
       </c>
       <c r="H12" t="str">
-        <v>2026-07 ($15000.00)</v>
+        <v/>
       </c>
     </row>
     <row r="13">
@@ -722,45 +723,45 @@
         <v>Bachata y Salsa Inicial</v>
       </c>
       <c r="C13" t="str">
-        <v>Histórica - Bachata y Salsa Inicial - 2026 - $40.000</v>
+        <v>Histórica - Bachata y Salsa Inicial - 2026 - $30.000</v>
       </c>
       <c r="D13" t="str">
-        <v>40000.00</v>
+        <v>30000.00</v>
       </c>
       <c r="E13" t="str">
-        <v>2026-08-01</v>
+        <v>2026-01-01</v>
       </c>
       <c r="F13" t="str">
-        <v>2026-08-31</v>
+        <v>2026-07-31</v>
       </c>
       <c r="G13" t="str">
-        <v>2026-08 = $40000.00</v>
+        <v>2026-05 = $30000.00</v>
       </c>
       <c r="H13" t="str">
-        <v/>
+        <v>2026-07 ($15000.00)</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>dbd5af21-ec55-4380-8ca1-d643a10d2003</v>
+        <v>acbbc26b-2a55-4952-97a0-92dc025024d2</v>
       </c>
       <c r="B14" t="str">
-        <v>Belly Dance Alternativo</v>
+        <v>Bachata y Salsa Inicial</v>
       </c>
       <c r="C14" t="str">
-        <v>Histórica - Belly Dance Alternativo - 2025 - $15.000</v>
+        <v>Histórica - Bachata y Salsa Inicial - 2026 - $40.000</v>
       </c>
       <c r="D14" t="str">
-        <v>15000.00</v>
+        <v>40000.00</v>
       </c>
       <c r="E14" t="str">
-        <v>2025-02-01</v>
+        <v>2026-08-01</v>
       </c>
       <c r="F14" t="str">
-        <v>2025-03-31</v>
+        <v>2026-08-31</v>
       </c>
       <c r="G14" t="str">
-        <v>2025-02 = $15000.00</v>
+        <v>2026-08 = $40000.00</v>
       </c>
       <c r="H14" t="str">
         <v/>
@@ -768,13 +769,13 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>d0762bb4-c6ef-45d4-8414-5ae0f158831f</v>
+        <v>dbd5af21-ec55-4380-8ca1-d643a10d2003</v>
       </c>
       <c r="B15" t="str">
-        <v>Clase femenino Sofi</v>
+        <v>Belly Dance Alternativo</v>
       </c>
       <c r="C15" t="str">
-        <v>Histórica - Clase femenino Sofi - 2025 - $15.000</v>
+        <v>Histórica - Belly Dance Alternativo - 2025 - $15.000</v>
       </c>
       <c r="D15" t="str">
         <v>15000.00</v>
@@ -826,19 +827,19 @@
         <v>Clase femenino Sofi</v>
       </c>
       <c r="C17" t="str">
-        <v>Histórica - Clase femenino Sofi - 2025 - $20.000</v>
+        <v>Histórica - Clase femenino Sofi - 2025 - $15.000</v>
       </c>
       <c r="D17" t="str">
-        <v>20000.00</v>
+        <v>15000.00</v>
       </c>
       <c r="E17" t="str">
-        <v>2025-03-01</v>
+        <v>2025-02-01</v>
       </c>
       <c r="F17" t="str">
-        <v>2025-08-31</v>
+        <v>2025-03-31</v>
       </c>
       <c r="G17" t="str">
-        <v>2025-03 = $20000.00</v>
+        <v>2025-02 = $15000.00</v>
       </c>
       <c r="H17" t="str">
         <v/>
@@ -858,16 +859,16 @@
         <v>20000.00</v>
       </c>
       <c r="E18" t="str">
-        <v>2025-04-01</v>
+        <v>2025-03-01</v>
       </c>
       <c r="F18" t="str">
-        <v>2025-08-31</v>
+        <v>2025-09-30</v>
       </c>
       <c r="G18" t="str">
-        <v>2025-04 = $20000.00</v>
+        <v>2025-03 = $20000.00 | 2025-04 = $20000.00</v>
       </c>
       <c r="H18" t="str">
-        <v/>
+        <v>2025-09 ($30000.00)</v>
       </c>
     </row>
     <row r="19">
@@ -878,22 +879,22 @@
         <v>Clase femenino Sofi</v>
       </c>
       <c r="C19" t="str">
-        <v>Histórica - Clase femenino Sofi - 2025 - $21.000</v>
+        <v>Histórica - Clase femenino Sofi - 2025 - $25.000</v>
       </c>
       <c r="D19" t="str">
-        <v>21000.00</v>
+        <v>25000.00</v>
       </c>
       <c r="E19" t="str">
-        <v>2025-09-01</v>
+        <v>2025-11-01</v>
       </c>
       <c r="F19" t="str">
-        <v>2025-09-30</v>
+        <v>2026-02-28</v>
       </c>
       <c r="G19" t="str">
-        <v>2025-09 = $21000.00</v>
+        <v>2025-11 = $25000.00</v>
       </c>
       <c r="H19" t="str">
-        <v/>
+        <v>2026-02 ($15000.00)</v>
       </c>
     </row>
     <row r="20">
@@ -904,22 +905,22 @@
         <v>Clase femenino Sofi</v>
       </c>
       <c r="C20" t="str">
-        <v>Histórica - Clase femenino Sofi - 2025 - $30.000</v>
+        <v>Histórica - Clase femenino Sofi - 2026 - $30.000</v>
       </c>
       <c r="D20" t="str">
         <v>30000.00</v>
       </c>
       <c r="E20" t="str">
-        <v>2025-09-01</v>
+        <v>2026-03-01</v>
       </c>
       <c r="F20" t="str">
-        <v>2025-10-31</v>
+        <v>2026-07-31</v>
       </c>
       <c r="G20" t="str">
-        <v>2025-09 = $30000.00</v>
+        <v>2026-03 = $30000.00 | 2026-05 = $30000.00 | 2026-05 = $30000.00</v>
       </c>
       <c r="H20" t="str">
-        <v/>
+        <v>2026-07 ($15000.00)</v>
       </c>
     </row>
     <row r="21">
@@ -930,19 +931,19 @@
         <v>Clase femenino Sofi</v>
       </c>
       <c r="C21" t="str">
-        <v>Histórica - Clase femenino Sofi - 2025 - $25.000</v>
+        <v>Histórica - Clase femenino Sofi - 2026 - $40.000</v>
       </c>
       <c r="D21" t="str">
-        <v>25000.00</v>
+        <v>40000.00</v>
       </c>
       <c r="E21" t="str">
-        <v>2025-11-01</v>
+        <v>2026-08-01</v>
       </c>
       <c r="F21" t="str">
-        <v>2025-11-30</v>
+        <v>2026-08-31</v>
       </c>
       <c r="G21" t="str">
-        <v>2025-11 = $25000.00</v>
+        <v>2026-08 = $40000.00 | 2026-08 = $40000.00</v>
       </c>
       <c r="H21" t="str">
         <v/>
@@ -950,25 +951,25 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>d0762bb4-c6ef-45d4-8414-5ae0f158831f</v>
+        <v>4074b25f-622a-4423-ac82-9d0cf90e3666</v>
       </c>
       <c r="B22" t="str">
-        <v>Clase femenino Sofi</v>
+        <v>Clase LT - A.Frank</v>
       </c>
       <c r="C22" t="str">
-        <v>Histórica - Clase femenino Sofi - 2026 - $30.000</v>
+        <v>Histórica - Clase LT - A.Frank - 2025 - $15.000</v>
       </c>
       <c r="D22" t="str">
-        <v>30000.00</v>
+        <v>15000.00</v>
       </c>
       <c r="E22" t="str">
-        <v>2026-02-01</v>
+        <v>2025-02-01</v>
       </c>
       <c r="F22" t="str">
-        <v>2026-03-31</v>
+        <v>2025-02-28</v>
       </c>
       <c r="G22" t="str">
-        <v>2026-02 = $30000.00</v>
+        <v>2025-02 = $15000.00</v>
       </c>
       <c r="H22" t="str">
         <v/>
@@ -976,25 +977,25 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>d0762bb4-c6ef-45d4-8414-5ae0f158831f</v>
+        <v>4074b25f-622a-4423-ac82-9d0cf90e3666</v>
       </c>
       <c r="B23" t="str">
-        <v>Clase femenino Sofi</v>
+        <v>Clase LT - A.Frank</v>
       </c>
       <c r="C23" t="str">
-        <v>Histórica - Clase femenino Sofi - 2026 - $15.000</v>
+        <v>Histórica - Clase LT - A.Frank - 2025 - $20.000</v>
       </c>
       <c r="D23" t="str">
-        <v>15000.00</v>
+        <v>20000.00</v>
       </c>
       <c r="E23" t="str">
-        <v>2026-02-01</v>
+        <v>2025-03-01</v>
       </c>
       <c r="F23" t="str">
-        <v>2026-02-28</v>
+        <v>2025-08-31</v>
       </c>
       <c r="G23" t="str">
-        <v>2026-02 = $15000.00</v>
+        <v>2025-03 = $20000.00</v>
       </c>
       <c r="H23" t="str">
         <v/>
@@ -1002,25 +1003,25 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>d0762bb4-c6ef-45d4-8414-5ae0f158831f</v>
+        <v>4074b25f-622a-4423-ac82-9d0cf90e3666</v>
       </c>
       <c r="B24" t="str">
-        <v>Clase femenino Sofi</v>
+        <v>Clase LT - A.Frank</v>
       </c>
       <c r="C24" t="str">
-        <v>Histórica - Clase femenino Sofi - 2026 - $30.000</v>
+        <v>Histórica - Clase LT - A.Frank - 2025 - $30.000</v>
       </c>
       <c r="D24" t="str">
         <v>30000.00</v>
       </c>
       <c r="E24" t="str">
-        <v>2026-03-01</v>
+        <v>2025-09-01</v>
       </c>
       <c r="F24" t="str">
-        <v>2026-03-31</v>
+        <v>2025-11-30</v>
       </c>
       <c r="G24" t="str">
-        <v>2026-03 = $30000.00</v>
+        <v>2025-09 = $30000.00</v>
       </c>
       <c r="H24" t="str">
         <v/>
@@ -1028,25 +1029,25 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>d0762bb4-c6ef-45d4-8414-5ae0f158831f</v>
+        <v>4074b25f-622a-4423-ac82-9d0cf90e3666</v>
       </c>
       <c r="B25" t="str">
-        <v>Clase femenino Sofi</v>
+        <v>Clase LT - A.Frank</v>
       </c>
       <c r="C25" t="str">
-        <v>Histórica - Clase femenino Sofi - 2026 - $30.000</v>
+        <v>Histórica - Clase LT - A.Frank - 2026 - $30.000</v>
       </c>
       <c r="D25" t="str">
         <v>30000.00</v>
       </c>
       <c r="E25" t="str">
-        <v>2026-05-01</v>
+        <v>2026-01-01</v>
       </c>
       <c r="F25" t="str">
         <v>2026-06-30</v>
       </c>
       <c r="G25" t="str">
-        <v>2026-05 = $30000.00</v>
+        <v>2026-01 = $30000.00 | 2026-05 = $30000.00</v>
       </c>
       <c r="H25" t="str">
         <v/>
@@ -1054,51 +1055,51 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>d0762bb4-c6ef-45d4-8414-5ae0f158831f</v>
+        <v>4074b25f-622a-4423-ac82-9d0cf90e3666</v>
       </c>
       <c r="B26" t="str">
-        <v>Clase femenino Sofi</v>
+        <v>Clase LT - A.Frank</v>
       </c>
       <c r="C26" t="str">
-        <v>Histórica - Clase femenino Sofi - 2026 - $30.000</v>
+        <v>Histórica - Clase LT - A.Frank - 2026 - $40.000</v>
       </c>
       <c r="D26" t="str">
-        <v>30000.00</v>
+        <v>40000.00</v>
       </c>
       <c r="E26" t="str">
-        <v>2026-05-01</v>
+        <v>2026-08-01</v>
       </c>
       <c r="F26" t="str">
-        <v>2026-07-31</v>
+        <v>2026-08-31</v>
       </c>
       <c r="G26" t="str">
-        <v>2026-05 = $30000.00</v>
+        <v>2026-08 = $40000.00</v>
       </c>
       <c r="H26" t="str">
-        <v>2026-07 ($15000.00)</v>
+        <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>d0762bb4-c6ef-45d4-8414-5ae0f158831f</v>
+        <v>28f1b214-f935-4bea-8a8c-a28789592bb0</v>
       </c>
       <c r="B27" t="str">
-        <v>Clase femenino Sofi</v>
+        <v>Coreográfico Bachata en Pareja</v>
       </c>
       <c r="C27" t="str">
-        <v>Histórica - Clase femenino Sofi - 2026 - $40.000</v>
+        <v>Histórica - Coreográfico Bachata en Pareja - 2025 - $20.000</v>
       </c>
       <c r="D27" t="str">
-        <v>40000.00</v>
+        <v>20000.00</v>
       </c>
       <c r="E27" t="str">
-        <v>2026-08-01</v>
+        <v>2025-05-01</v>
       </c>
       <c r="F27" t="str">
-        <v>2026-08-31</v>
+        <v>2025-05-31</v>
       </c>
       <c r="G27" t="str">
-        <v>2026-08 = $40000.00</v>
+        <v>2025-05 = $20000.00</v>
       </c>
       <c r="H27" t="str">
         <v/>
@@ -1106,25 +1107,25 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>d0762bb4-c6ef-45d4-8414-5ae0f158831f</v>
+        <v>28f1b214-f935-4bea-8a8c-a28789592bb0</v>
       </c>
       <c r="B28" t="str">
-        <v>Clase femenino Sofi</v>
+        <v>Coreográfico Bachata en Pareja</v>
       </c>
       <c r="C28" t="str">
-        <v>Histórica - Clase femenino Sofi - 2026 - $40.000</v>
+        <v>Histórica - Coreográfico Bachata en Pareja - 2025 - $10.000</v>
       </c>
       <c r="D28" t="str">
-        <v>40000.00</v>
+        <v>10000.00</v>
       </c>
       <c r="E28" t="str">
-        <v>2026-08-01</v>
+        <v>2025-06-01</v>
       </c>
       <c r="F28" t="str">
-        <v>2026-08-31</v>
+        <v>2025-06-30</v>
       </c>
       <c r="G28" t="str">
-        <v>2026-08 = $40000.00</v>
+        <v>2025-06 = $10000.00</v>
       </c>
       <c r="H28" t="str">
         <v/>
@@ -1132,16 +1133,16 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>4074b25f-622a-4423-ac82-9d0cf90e3666</v>
+        <v>db1e0e5e-c5e0-429e-aec3-4f28d406dad9</v>
       </c>
       <c r="B29" t="str">
-        <v>Clase LT - A.Frank</v>
+        <v>Fitdance + Axé</v>
       </c>
       <c r="C29" t="str">
-        <v>Histórica - Clase LT - A.Frank - 2025 - $15.000</v>
+        <v>Histórica - Fitdance + Axé - 2025 - $7.500</v>
       </c>
       <c r="D29" t="str">
-        <v>15000.00</v>
+        <v>7500.00</v>
       </c>
       <c r="E29" t="str">
         <v>2025-02-01</v>
@@ -1150,7 +1151,7 @@
         <v>2025-02-28</v>
       </c>
       <c r="G29" t="str">
-        <v>2025-02 = $15000.00</v>
+        <v>2025-02 = $7500.00</v>
       </c>
       <c r="H29" t="str">
         <v/>
@@ -1158,25 +1159,25 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>4074b25f-622a-4423-ac82-9d0cf90e3666</v>
+        <v>e63b18a1-afc2-4fd1-aa80-dfce8909e30f</v>
       </c>
       <c r="B30" t="str">
-        <v>Clase LT - A.Frank</v>
+        <v>Grupo C. - A.Frank</v>
       </c>
       <c r="C30" t="str">
-        <v>Histórica - Clase LT - A.Frank - 2025 - $20.000</v>
+        <v>Histórica - Grupo C. - A.Frank - 2026 - $25.000</v>
       </c>
       <c r="D30" t="str">
-        <v>20000.00</v>
+        <v>25000.00</v>
       </c>
       <c r="E30" t="str">
-        <v>2025-03-01</v>
+        <v>2026-03-01</v>
       </c>
       <c r="F30" t="str">
-        <v>2025-08-31</v>
+        <v>2026-06-30</v>
       </c>
       <c r="G30" t="str">
-        <v>2025-03 = $20000.00</v>
+        <v>2026-03 = $25000.00 | 2026-05 = $25000.00</v>
       </c>
       <c r="H30" t="str">
         <v/>
@@ -1184,25 +1185,25 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>4074b25f-622a-4423-ac82-9d0cf90e3666</v>
+        <v>bcea570e-e3dd-499f-8a4b-88f079773871</v>
       </c>
       <c r="B31" t="str">
-        <v>Clase LT - A.Frank</v>
+        <v>Infantil (6 a 7 años)</v>
       </c>
       <c r="C31" t="str">
-        <v>Histórica - Clase LT - A.Frank - 2025 - $30.000</v>
+        <v>Histórica - Infantil (6 a 7 años) - 2025 - $15.000</v>
       </c>
       <c r="D31" t="str">
-        <v>30000.00</v>
+        <v>15000.00</v>
       </c>
       <c r="E31" t="str">
-        <v>2025-09-01</v>
+        <v>2025-02-01</v>
       </c>
       <c r="F31" t="str">
-        <v>2025-11-30</v>
+        <v>2025-02-28</v>
       </c>
       <c r="G31" t="str">
-        <v>2025-09 = $30000.00</v>
+        <v>2025-02 = $15000.00</v>
       </c>
       <c r="H31" t="str">
         <v/>
@@ -1210,25 +1211,25 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>4074b25f-622a-4423-ac82-9d0cf90e3666</v>
+        <v>bcea570e-e3dd-499f-8a4b-88f079773871</v>
       </c>
       <c r="B32" t="str">
-        <v>Clase LT - A.Frank</v>
+        <v>Infantil (6 a 7 años)</v>
       </c>
       <c r="C32" t="str">
-        <v>Histórica - Clase LT - A.Frank - 2026 - $30.000</v>
+        <v>Histórica - Infantil (6 a 7 años) - 2025 - $20.000</v>
       </c>
       <c r="D32" t="str">
-        <v>30000.00</v>
+        <v>20000.00</v>
       </c>
       <c r="E32" t="str">
-        <v>2026-01-01</v>
+        <v>2025-03-01</v>
       </c>
       <c r="F32" t="str">
-        <v>2026-03-31</v>
+        <v>2025-08-31</v>
       </c>
       <c r="G32" t="str">
-        <v>2026-01 = $30000.00</v>
+        <v>2025-03 = $20000.00</v>
       </c>
       <c r="H32" t="str">
         <v/>
@@ -1236,25 +1237,25 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>4074b25f-622a-4423-ac82-9d0cf90e3666</v>
+        <v>bcea570e-e3dd-499f-8a4b-88f079773871</v>
       </c>
       <c r="B33" t="str">
-        <v>Clase LT - A.Frank</v>
+        <v>Infantil (6 a 7 años)</v>
       </c>
       <c r="C33" t="str">
-        <v>Histórica - Clase LT - A.Frank - 2026 - $30.000</v>
+        <v>Histórica - Infantil (6 a 7 años) - 2025 - $30.000</v>
       </c>
       <c r="D33" t="str">
         <v>30000.00</v>
       </c>
       <c r="E33" t="str">
-        <v>2026-05-01</v>
+        <v>2025-09-01</v>
       </c>
       <c r="F33" t="str">
-        <v>2026-06-30</v>
+        <v>2025-11-30</v>
       </c>
       <c r="G33" t="str">
-        <v>2026-05 = $30000.00</v>
+        <v>2025-09 = $30000.00</v>
       </c>
       <c r="H33" t="str">
         <v/>
@@ -1262,51 +1263,51 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>4074b25f-622a-4423-ac82-9d0cf90e3666</v>
+        <v>bcea570e-e3dd-499f-8a4b-88f079773871</v>
       </c>
       <c r="B34" t="str">
-        <v>Clase LT - A.Frank</v>
+        <v>Infantil (6 a 7 años)</v>
       </c>
       <c r="C34" t="str">
-        <v>Histórica - Clase LT - A.Frank - 2026 - $40.000</v>
+        <v>Histórica - Infantil (6 a 7 años) - 2026 - $30.000</v>
       </c>
       <c r="D34" t="str">
-        <v>40000.00</v>
+        <v>30000.00</v>
       </c>
       <c r="E34" t="str">
-        <v>2026-08-01</v>
+        <v>2026-01-01</v>
       </c>
       <c r="F34" t="str">
-        <v>2026-08-31</v>
+        <v>2026-07-31</v>
       </c>
       <c r="G34" t="str">
-        <v>2026-08 = $40000.00</v>
+        <v>2026-01 = $30000.00 | 2026-05 = $30000.00</v>
       </c>
       <c r="H34" t="str">
-        <v/>
+        <v>2026-07 ($15000.00)</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>28f1b214-f935-4bea-8a8c-a28789592bb0</v>
+        <v>bcea570e-e3dd-499f-8a4b-88f079773871</v>
       </c>
       <c r="B35" t="str">
-        <v>Coreográfico Bachata en Pareja</v>
+        <v>Infantil (6 a 7 años)</v>
       </c>
       <c r="C35" t="str">
-        <v>Histórica - Coreográfico Bachata en Pareja - 2025 - $20.000</v>
+        <v>Histórica - Infantil (6 a 7 años) - 2026 - $40.000</v>
       </c>
       <c r="D35" t="str">
-        <v>20000.00</v>
+        <v>40000.00</v>
       </c>
       <c r="E35" t="str">
-        <v>2025-05-01</v>
+        <v>2026-08-01</v>
       </c>
       <c r="F35" t="str">
-        <v>2025-05-31</v>
+        <v>2026-08-31</v>
       </c>
       <c r="G35" t="str">
-        <v>2025-05 = $20000.00</v>
+        <v>2026-08 = $40000.00</v>
       </c>
       <c r="H35" t="str">
         <v/>
@@ -1314,25 +1315,25 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>28f1b214-f935-4bea-8a8c-a28789592bb0</v>
+        <v>4cd54a73-4b21-4bd6-ae3f-7008b4e51e4a</v>
       </c>
       <c r="B36" t="str">
-        <v>Coreográfico Bachata en Pareja</v>
+        <v>Kids 4-5 años</v>
       </c>
       <c r="C36" t="str">
-        <v>Histórica - Coreográfico Bachata en Pareja - 2025 - $10.000</v>
+        <v>Histórica - Kids 4-5 años - 2025 - $20.000</v>
       </c>
       <c r="D36" t="str">
-        <v>10000.00</v>
+        <v>20000.00</v>
       </c>
       <c r="E36" t="str">
-        <v>2025-06-01</v>
+        <v>2025-05-01</v>
       </c>
       <c r="F36" t="str">
-        <v>2025-06-30</v>
+        <v>2025-08-31</v>
       </c>
       <c r="G36" t="str">
-        <v>2025-06 = $10000.00</v>
+        <v>2025-05 = $20000.00</v>
       </c>
       <c r="H36" t="str">
         <v/>
@@ -1340,25 +1341,25 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>db1e0e5e-c5e0-429e-aec3-4f28d406dad9</v>
+        <v>4cd54a73-4b21-4bd6-ae3f-7008b4e51e4a</v>
       </c>
       <c r="B37" t="str">
-        <v>Fitdance + Axé</v>
+        <v>Kids 4-5 años</v>
       </c>
       <c r="C37" t="str">
-        <v>Histórica - Fitdance + Axé - 2025 - $7.500</v>
+        <v>Histórica - Kids 4-5 años - 2025 - $30.000</v>
       </c>
       <c r="D37" t="str">
-        <v>7500.00</v>
+        <v>30000.00</v>
       </c>
       <c r="E37" t="str">
-        <v>2025-02-01</v>
+        <v>2025-09-01</v>
       </c>
       <c r="F37" t="str">
-        <v>2025-02-28</v>
+        <v>2025-11-30</v>
       </c>
       <c r="G37" t="str">
-        <v>2025-02 = $7500.00</v>
+        <v/>
       </c>
       <c r="H37" t="str">
         <v/>
@@ -1366,51 +1367,51 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>e63b18a1-afc2-4fd1-aa80-dfce8909e30f</v>
+        <v>4cd54a73-4b21-4bd6-ae3f-7008b4e51e4a</v>
       </c>
       <c r="B38" t="str">
-        <v>Grupo C. - A.Frank</v>
+        <v>Kids 4-5 años</v>
       </c>
       <c r="C38" t="str">
-        <v>Histórica - Grupo C. - A.Frank - 2026 - $25.000</v>
+        <v>Histórica - Kids 4-5 años - 2026 - $30.000</v>
       </c>
       <c r="D38" t="str">
-        <v>25000.00</v>
+        <v>30000.00</v>
       </c>
       <c r="E38" t="str">
-        <v>2026-03-01</v>
+        <v>2026-01-01</v>
       </c>
       <c r="F38" t="str">
-        <v>2026-03-31</v>
+        <v>2026-07-31</v>
       </c>
       <c r="G38" t="str">
-        <v>2026-03 = $25000.00</v>
+        <v>2026-01 = $30000.00 | 2026-05 = $30000.00</v>
       </c>
       <c r="H38" t="str">
-        <v/>
+        <v>2026-07 ($15000.00)</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>e63b18a1-afc2-4fd1-aa80-dfce8909e30f</v>
+        <v>4cd54a73-4b21-4bd6-ae3f-7008b4e51e4a</v>
       </c>
       <c r="B39" t="str">
-        <v>Grupo C. - A.Frank</v>
+        <v>Kids 4-5 años</v>
       </c>
       <c r="C39" t="str">
-        <v>Histórica - Grupo C. - A.Frank - 2026 - $25.000</v>
+        <v>Histórica - Kids 4-5 años - 2026 - $40.000</v>
       </c>
       <c r="D39" t="str">
-        <v>25000.00</v>
+        <v>40000.00</v>
       </c>
       <c r="E39" t="str">
-        <v>2026-05-01</v>
+        <v>2026-08-01</v>
       </c>
       <c r="F39" t="str">
-        <v>2026-06-30</v>
+        <v>2026-08-31</v>
       </c>
       <c r="G39" t="str">
-        <v>2026-05 = $25000.00</v>
+        <v>2026-08 = $40000.00</v>
       </c>
       <c r="H39" t="str">
         <v/>
@@ -1418,16 +1419,16 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>bcea570e-e3dd-499f-8a4b-88f079773871</v>
+        <v>06f93e1a-5cc0-4741-8ad6-813745ea389d</v>
       </c>
       <c r="B40" t="str">
-        <v>Infantil (6 a 7 años)</v>
+        <v>Ladys Kizz</v>
       </c>
       <c r="C40" t="str">
-        <v>Histórica - Infantil (6 a 7 años) - 2025 - $15.000</v>
+        <v>Histórica - Ladys Kizz - 2025 - $7.500</v>
       </c>
       <c r="D40" t="str">
-        <v>15000.00</v>
+        <v>7500.00</v>
       </c>
       <c r="E40" t="str">
         <v>2025-02-01</v>
@@ -1436,7 +1437,7 @@
         <v>2025-02-28</v>
       </c>
       <c r="G40" t="str">
-        <v>2025-02 = $15000.00</v>
+        <v>2025-02 = $7500.00</v>
       </c>
       <c r="H40" t="str">
         <v/>
@@ -1444,13 +1445,13 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>bcea570e-e3dd-499f-8a4b-88f079773871</v>
+        <v>06f93e1a-5cc0-4741-8ad6-813745ea389d</v>
       </c>
       <c r="B41" t="str">
-        <v>Infantil (6 a 7 años)</v>
+        <v>Ladys Kizz</v>
       </c>
       <c r="C41" t="str">
-        <v>Histórica - Infantil (6 a 7 años) - 2025 - $20.000</v>
+        <v>Histórica - Ladys Kizz - 2025 - $20.000</v>
       </c>
       <c r="D41" t="str">
         <v>20000.00</v>
@@ -1459,7 +1460,7 @@
         <v>2025-03-01</v>
       </c>
       <c r="F41" t="str">
-        <v>2025-08-31</v>
+        <v>2025-07-31</v>
       </c>
       <c r="G41" t="str">
         <v>2025-03 = $20000.00</v>
@@ -1470,25 +1471,25 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>bcea570e-e3dd-499f-8a4b-88f079773871</v>
+        <v>a12f5acf-4754-479a-853c-15926c2dac92</v>
       </c>
       <c r="B42" t="str">
-        <v>Infantil (6 a 7 años)</v>
+        <v>Ladys Tango - Gabriela P.</v>
       </c>
       <c r="C42" t="str">
-        <v>Histórica - Infantil (6 a 7 años) - 2025 - $30.000</v>
+        <v>Histórica - Ladys Tango - Gabriela P. - 2025 - $7.500</v>
       </c>
       <c r="D42" t="str">
-        <v>30000.00</v>
+        <v>7500.00</v>
       </c>
       <c r="E42" t="str">
-        <v>2025-09-01</v>
+        <v>2025-02-01</v>
       </c>
       <c r="F42" t="str">
-        <v>2025-11-30</v>
+        <v>2025-02-28</v>
       </c>
       <c r="G42" t="str">
-        <v>2025-09 = $30000.00</v>
+        <v>2025-02 = $7500.00</v>
       </c>
       <c r="H42" t="str">
         <v/>
@@ -1496,25 +1497,25 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>bcea570e-e3dd-499f-8a4b-88f079773871</v>
+        <v>a12f5acf-4754-479a-853c-15926c2dac92</v>
       </c>
       <c r="B43" t="str">
-        <v>Infantil (6 a 7 años)</v>
+        <v>Ladys Tango - Gabriela P.</v>
       </c>
       <c r="C43" t="str">
-        <v>Histórica - Infantil (6 a 7 años) - 2026 - $30.000</v>
+        <v>Histórica - Ladys Tango - Gabriela P. - 2025 - $10.000</v>
       </c>
       <c r="D43" t="str">
-        <v>30000.00</v>
+        <v>10000.00</v>
       </c>
       <c r="E43" t="str">
-        <v>2026-01-01</v>
+        <v>2025-03-01</v>
       </c>
       <c r="F43" t="str">
-        <v>2026-03-31</v>
+        <v>2025-04-30</v>
       </c>
       <c r="G43" t="str">
-        <v>2026-01 = $30000.00</v>
+        <v>2025-03 = $10000.00</v>
       </c>
       <c r="H43" t="str">
         <v/>
@@ -1522,51 +1523,51 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>bcea570e-e3dd-499f-8a4b-88f079773871</v>
+        <v>a12f5acf-4754-479a-853c-15926c2dac92</v>
       </c>
       <c r="B44" t="str">
-        <v>Infantil (6 a 7 años)</v>
+        <v>Ladys Tango - Gabriela P.</v>
       </c>
       <c r="C44" t="str">
-        <v>Histórica - Infantil (6 a 7 años) - 2026 - $30.000</v>
+        <v>Histórica - Ladys Tango - Gabriela P. - 2025 - $11.000</v>
       </c>
       <c r="D44" t="str">
-        <v>30000.00</v>
+        <v>11000.00</v>
       </c>
       <c r="E44" t="str">
-        <v>2026-05-01</v>
+        <v>2025-05-01</v>
       </c>
       <c r="F44" t="str">
-        <v>2026-07-31</v>
+        <v>2025-06-30</v>
       </c>
       <c r="G44" t="str">
-        <v>2026-05 = $30000.00</v>
+        <v>2025-05 = $11000.00</v>
       </c>
       <c r="H44" t="str">
-        <v>2026-07 ($15000.00)</v>
+        <v/>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>bcea570e-e3dd-499f-8a4b-88f079773871</v>
+        <v>a12f5acf-4754-479a-853c-15926c2dac92</v>
       </c>
       <c r="B45" t="str">
-        <v>Infantil (6 a 7 años)</v>
+        <v>Ladys Tango - Gabriela P.</v>
       </c>
       <c r="C45" t="str">
-        <v>Histórica - Infantil (6 a 7 años) - 2026 - $40.000</v>
+        <v>Histórica - Ladys Tango - Gabriela P. - 2025 - $20.000</v>
       </c>
       <c r="D45" t="str">
-        <v>40000.00</v>
+        <v>20000.00</v>
       </c>
       <c r="E45" t="str">
-        <v>2026-08-01</v>
+        <v>2025-07-01</v>
       </c>
       <c r="F45" t="str">
-        <v>2026-08-31</v>
+        <v>2025-07-31</v>
       </c>
       <c r="G45" t="str">
-        <v>2026-08 = $40000.00</v>
+        <v>2025-07 = $20000.00</v>
       </c>
       <c r="H45" t="str">
         <v/>
@@ -1574,25 +1575,25 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>4cd54a73-4b21-4bd6-ae3f-7008b4e51e4a</v>
+        <v>b96017bd-9ee1-4bde-ad35-ad961a78e5f5</v>
       </c>
       <c r="B46" t="str">
-        <v>Kids 4-5 años</v>
+        <v>Mambo en parejas</v>
       </c>
       <c r="C46" t="str">
-        <v>Histórica - Kids 4-5 años - 2025 - $20.000</v>
+        <v>Histórica - Mambo en parejas - 2026 - $15.000</v>
       </c>
       <c r="D46" t="str">
-        <v>20000.00</v>
+        <v>15000.00</v>
       </c>
       <c r="E46" t="str">
-        <v>2025-05-01</v>
+        <v>2026-02-01</v>
       </c>
       <c r="F46" t="str">
-        <v>2025-07-31</v>
+        <v>2026-02-28</v>
       </c>
       <c r="G46" t="str">
-        <v>2025-05 = $20000.00</v>
+        <v>2026-02 = $15000.00</v>
       </c>
       <c r="H46" t="str">
         <v/>
@@ -1600,77 +1601,77 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>4cd54a73-4b21-4bd6-ae3f-7008b4e51e4a</v>
+        <v>b96017bd-9ee1-4bde-ad35-ad961a78e5f5</v>
       </c>
       <c r="B47" t="str">
-        <v>Kids 4-5 años</v>
+        <v>Mambo en parejas</v>
       </c>
       <c r="C47" t="str">
-        <v>Histórica - Kids 4-5 años - 2026 - $30.000</v>
+        <v>Histórica - Mambo en parejas - 2026 - $30.000</v>
       </c>
       <c r="D47" t="str">
         <v>30000.00</v>
       </c>
       <c r="E47" t="str">
-        <v>2026-01-01</v>
+        <v>2026-03-01</v>
       </c>
       <c r="F47" t="str">
-        <v>2026-03-31</v>
+        <v>2026-07-31</v>
       </c>
       <c r="G47" t="str">
-        <v>2026-01 = $30000.00</v>
+        <v>2026-03 = $30000.00 | 2026-05 = $30000.00</v>
       </c>
       <c r="H47" t="str">
-        <v/>
+        <v>2026-07 ($15000.00)</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>4cd54a73-4b21-4bd6-ae3f-7008b4e51e4a</v>
+        <v>b96017bd-9ee1-4bde-ad35-ad961a78e5f5</v>
       </c>
       <c r="B48" t="str">
-        <v>Kids 4-5 años</v>
+        <v>Mambo en parejas</v>
       </c>
       <c r="C48" t="str">
-        <v>Histórica - Kids 4-5 años - 2026 - $30.000</v>
+        <v>Histórica - Mambo en parejas - 2026 - $40.000</v>
       </c>
       <c r="D48" t="str">
-        <v>30000.00</v>
+        <v>40000.00</v>
       </c>
       <c r="E48" t="str">
-        <v>2026-05-01</v>
+        <v>2026-08-01</v>
       </c>
       <c r="F48" t="str">
-        <v>2026-07-31</v>
+        <v>2026-08-31</v>
       </c>
       <c r="G48" t="str">
-        <v>2026-05 = $30000.00</v>
+        <v>2026-08 = $40000.00</v>
       </c>
       <c r="H48" t="str">
-        <v>2026-07 ($15000.00)</v>
+        <v/>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>4cd54a73-4b21-4bd6-ae3f-7008b4e51e4a</v>
+        <v>1a8e1c0e-1f96-4de2-a33d-c932e74f2314</v>
       </c>
       <c r="B49" t="str">
-        <v>Kids 4-5 años</v>
+        <v>Ritmos latinos y caribeños</v>
       </c>
       <c r="C49" t="str">
-        <v>Histórica - Kids 4-5 años - 2026 - $40.000</v>
+        <v>Histórica - Ritmos latinos y caribeños - 2025 - $15.000</v>
       </c>
       <c r="D49" t="str">
-        <v>40000.00</v>
+        <v>15000.00</v>
       </c>
       <c r="E49" t="str">
-        <v>2026-08-01</v>
+        <v>2025-02-01</v>
       </c>
       <c r="F49" t="str">
-        <v>2026-08-31</v>
+        <v>2025-02-28</v>
       </c>
       <c r="G49" t="str">
-        <v>2026-08 = $40000.00</v>
+        <v>2025-02 = $15000.00</v>
       </c>
       <c r="H49" t="str">
         <v/>
@@ -1678,25 +1679,25 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>06f93e1a-5cc0-4741-8ad6-813745ea389d</v>
+        <v>1a8e1c0e-1f96-4de2-a33d-c932e74f2314</v>
       </c>
       <c r="B50" t="str">
-        <v>Ladys Kizz</v>
+        <v>Ritmos latinos y caribeños</v>
       </c>
       <c r="C50" t="str">
-        <v>Histórica - Ladys Kizz - 2025 - $7.500</v>
+        <v>Histórica - Ritmos latinos y caribeños - 2025 - $20.000</v>
       </c>
       <c r="D50" t="str">
-        <v>7500.00</v>
+        <v>20000.00</v>
       </c>
       <c r="E50" t="str">
-        <v>2025-02-01</v>
+        <v>2025-03-01</v>
       </c>
       <c r="F50" t="str">
-        <v>2025-02-28</v>
+        <v>2025-07-31</v>
       </c>
       <c r="G50" t="str">
-        <v>2025-02 = $7500.00</v>
+        <v>2025-03 = $20000.00</v>
       </c>
       <c r="H50" t="str">
         <v/>
@@ -1704,25 +1705,25 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>06f93e1a-5cc0-4741-8ad6-813745ea389d</v>
+        <v>71bc486f-8a3d-46bb-a102-838cfef0a1fc</v>
       </c>
       <c r="B51" t="str">
-        <v>Ladys Kizz</v>
+        <v>S.C Adultos (+18 años)</v>
       </c>
       <c r="C51" t="str">
-        <v>Histórica - Ladys Kizz - 2025 - $20.000</v>
+        <v>Histórica - S.C Adultos (+18 años) - 2025 - $15.000</v>
       </c>
       <c r="D51" t="str">
-        <v>20000.00</v>
+        <v>15000.00</v>
       </c>
       <c r="E51" t="str">
-        <v>2025-03-01</v>
+        <v>2025-02-01</v>
       </c>
       <c r="F51" t="str">
-        <v>2025-07-31</v>
+        <v>2025-02-28</v>
       </c>
       <c r="G51" t="str">
-        <v>2025-03 = $20000.00</v>
+        <v>2025-02 = $15000.00</v>
       </c>
       <c r="H51" t="str">
         <v/>
@@ -1730,25 +1731,25 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>a12f5acf-4754-479a-853c-15926c2dac92</v>
+        <v>71bc486f-8a3d-46bb-a102-838cfef0a1fc</v>
       </c>
       <c r="B52" t="str">
-        <v>Ladys Tango - Gabriela P.</v>
+        <v>S.C Adultos (+18 años)</v>
       </c>
       <c r="C52" t="str">
-        <v>Histórica - Ladys Tango - Gabriela P. - 2025 - $7.500</v>
+        <v>Histórica - S.C Adultos (+18 años) - 2025 - $20.000</v>
       </c>
       <c r="D52" t="str">
-        <v>7500.00</v>
+        <v>20000.00</v>
       </c>
       <c r="E52" t="str">
-        <v>2025-02-01</v>
+        <v>2025-03-01</v>
       </c>
       <c r="F52" t="str">
-        <v>2025-02-28</v>
+        <v>2025-04-30</v>
       </c>
       <c r="G52" t="str">
-        <v>2025-02 = $7500.00</v>
+        <v>2025-03 = $20000.00</v>
       </c>
       <c r="H52" t="str">
         <v/>
@@ -1756,25 +1757,25 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>a12f5acf-4754-479a-853c-15926c2dac92</v>
+        <v>4b2663bf-5ab4-42e5-865c-2af4da2cf5ff</v>
       </c>
       <c r="B53" t="str">
-        <v>Ladys Tango - Gabriela P.</v>
+        <v>S.C Infantil (6-11 años)</v>
       </c>
       <c r="C53" t="str">
-        <v>Histórica - Ladys Tango - Gabriela P. - 2025 - $10.000</v>
+        <v>Histórica - S.C Infantil (6-11 años) - 2025 - $15.000</v>
       </c>
       <c r="D53" t="str">
-        <v>10000.00</v>
+        <v>15000.00</v>
       </c>
       <c r="E53" t="str">
-        <v>2025-03-01</v>
+        <v>2025-02-01</v>
       </c>
       <c r="F53" t="str">
-        <v>2025-04-30</v>
+        <v>2025-02-28</v>
       </c>
       <c r="G53" t="str">
-        <v>2025-03 = $10000.00</v>
+        <v>2025-02 = $15000.00</v>
       </c>
       <c r="H53" t="str">
         <v/>
@@ -1782,25 +1783,25 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>a12f5acf-4754-479a-853c-15926c2dac92</v>
+        <v>4b2663bf-5ab4-42e5-865c-2af4da2cf5ff</v>
       </c>
       <c r="B54" t="str">
-        <v>Ladys Tango - Gabriela P.</v>
+        <v>S.C Infantil (6-11 años)</v>
       </c>
       <c r="C54" t="str">
-        <v>Histórica - Ladys Tango - Gabriela P. - 2025 - $11.000</v>
+        <v>Histórica - S.C Infantil (6-11 años) - 2025 - $20.000</v>
       </c>
       <c r="D54" t="str">
-        <v>11000.00</v>
+        <v>20000.00</v>
       </c>
       <c r="E54" t="str">
-        <v>2025-05-01</v>
+        <v>2025-03-01</v>
       </c>
       <c r="F54" t="str">
-        <v>2025-06-30</v>
+        <v>2025-04-30</v>
       </c>
       <c r="G54" t="str">
-        <v>2025-05 = $11000.00</v>
+        <v>2025-03 = $20000.00</v>
       </c>
       <c r="H54" t="str">
         <v/>
@@ -1808,25 +1809,25 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>a12f5acf-4754-479a-853c-15926c2dac92</v>
+        <v>f8a32bf2-9e2a-48b5-9f2e-a8b9da860fb3</v>
       </c>
       <c r="B55" t="str">
-        <v>Ladys Tango - Gabriela P.</v>
+        <v>S.C Juvenil (12-17 años)</v>
       </c>
       <c r="C55" t="str">
-        <v>Histórica - Ladys Tango - Gabriela P. - 2025 - $20.000</v>
+        <v>Histórica - S.C Juvenil (12-17 años) - 2025 - $15.000</v>
       </c>
       <c r="D55" t="str">
-        <v>20000.00</v>
+        <v>15000.00</v>
       </c>
       <c r="E55" t="str">
-        <v>2025-07-01</v>
+        <v>2025-02-01</v>
       </c>
       <c r="F55" t="str">
-        <v>2025-07-31</v>
+        <v>2025-02-28</v>
       </c>
       <c r="G55" t="str">
-        <v>2025-07 = $20000.00</v>
+        <v>2025-02 = $15000.00</v>
       </c>
       <c r="H55" t="str">
         <v/>
@@ -1834,25 +1835,25 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>b96017bd-9ee1-4bde-ad35-ad961a78e5f5</v>
+        <v>f8a32bf2-9e2a-48b5-9f2e-a8b9da860fb3</v>
       </c>
       <c r="B56" t="str">
-        <v>Mambo en parejas</v>
+        <v>S.C Juvenil (12-17 años)</v>
       </c>
       <c r="C56" t="str">
-        <v>Histórica - Mambo en parejas - 2026 - $15.000</v>
+        <v>Histórica - S.C Juvenil (12-17 años) - 2025 - $20.000</v>
       </c>
       <c r="D56" t="str">
-        <v>15000.00</v>
+        <v>20000.00</v>
       </c>
       <c r="E56" t="str">
-        <v>2026-02-01</v>
+        <v>2025-03-01</v>
       </c>
       <c r="F56" t="str">
-        <v>2026-02-28</v>
+        <v>2025-04-30</v>
       </c>
       <c r="G56" t="str">
-        <v>2026-02 = $15000.00</v>
+        <v>2025-03 = $20000.00</v>
       </c>
       <c r="H56" t="str">
         <v/>
@@ -1860,25 +1861,25 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>b96017bd-9ee1-4bde-ad35-ad961a78e5f5</v>
+        <v>dd4b0323-e82f-4b02-89c0-0f8e520033ed</v>
       </c>
       <c r="B57" t="str">
-        <v>Mambo en parejas</v>
+        <v>Street Int/Avanzado</v>
       </c>
       <c r="C57" t="str">
-        <v>Histórica - Mambo en parejas - 2026 - $30.000</v>
+        <v>Histórica - Street Int/Avanzado - 2025 - $15.000</v>
       </c>
       <c r="D57" t="str">
-        <v>30000.00</v>
+        <v>15000.00</v>
       </c>
       <c r="E57" t="str">
-        <v>2026-03-01</v>
+        <v>2025-02-01</v>
       </c>
       <c r="F57" t="str">
-        <v>2026-03-31</v>
+        <v>2025-02-28</v>
       </c>
       <c r="G57" t="str">
-        <v>2026-03 = $30000.00</v>
+        <v>2025-02 = $15000.00</v>
       </c>
       <c r="H57" t="str">
         <v/>
@@ -1886,51 +1887,51 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>b96017bd-9ee1-4bde-ad35-ad961a78e5f5</v>
+        <v>dd4b0323-e82f-4b02-89c0-0f8e520033ed</v>
       </c>
       <c r="B58" t="str">
-        <v>Mambo en parejas</v>
+        <v>Street Int/Avanzado</v>
       </c>
       <c r="C58" t="str">
-        <v>Histórica - Mambo en parejas - 2026 - $30.000</v>
+        <v>Histórica - Street Int/Avanzado - 2025 - $20.000</v>
       </c>
       <c r="D58" t="str">
-        <v>30000.00</v>
+        <v>20000.00</v>
       </c>
       <c r="E58" t="str">
-        <v>2026-05-01</v>
+        <v>2025-03-01</v>
       </c>
       <c r="F58" t="str">
-        <v>2026-07-31</v>
+        <v>2025-04-30</v>
       </c>
       <c r="G58" t="str">
-        <v>2026-05 = $30000.00</v>
+        <v>2025-03 = $20000.00</v>
       </c>
       <c r="H58" t="str">
-        <v>2026-07 ($15000.00)</v>
+        <v/>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>b96017bd-9ee1-4bde-ad35-ad961a78e5f5</v>
+        <v>cc392129-75e3-4205-b7fc-fafceb55b996</v>
       </c>
       <c r="B59" t="str">
-        <v>Mambo en parejas</v>
+        <v>Tango (Inter/Avanz)</v>
       </c>
       <c r="C59" t="str">
-        <v>Histórica - Mambo en parejas - 2026 - $40.000</v>
+        <v>Histórica - Tango (Inter/Avanz) - 2025 - $15.000</v>
       </c>
       <c r="D59" t="str">
-        <v>40000.00</v>
+        <v>15000.00</v>
       </c>
       <c r="E59" t="str">
-        <v>2026-08-01</v>
+        <v>2025-02-01</v>
       </c>
       <c r="F59" t="str">
-        <v>2026-08-31</v>
+        <v>2025-02-28</v>
       </c>
       <c r="G59" t="str">
-        <v>2026-08 = $40000.00</v>
+        <v>2025-02 = $15000.00</v>
       </c>
       <c r="H59" t="str">
         <v/>
@@ -1938,25 +1939,25 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>1a8e1c0e-1f96-4de2-a33d-c932e74f2314</v>
+        <v>cc392129-75e3-4205-b7fc-fafceb55b996</v>
       </c>
       <c r="B60" t="str">
-        <v>Ritmos latinos y caribeños</v>
+        <v>Tango (Inter/Avanz)</v>
       </c>
       <c r="C60" t="str">
-        <v>Histórica - Ritmos latinos y caribeños - 2025 - $15.000</v>
+        <v>Histórica - Tango (Inter/Avanz) - 2025 - $20.000</v>
       </c>
       <c r="D60" t="str">
-        <v>15000.00</v>
+        <v>20000.00</v>
       </c>
       <c r="E60" t="str">
-        <v>2025-02-01</v>
+        <v>2025-03-01</v>
       </c>
       <c r="F60" t="str">
-        <v>2025-02-28</v>
+        <v>2025-08-31</v>
       </c>
       <c r="G60" t="str">
-        <v>2025-02 = $15000.00</v>
+        <v>2025-03 = $20000.00</v>
       </c>
       <c r="H60" t="str">
         <v/>
@@ -1964,25 +1965,25 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>1a8e1c0e-1f96-4de2-a33d-c932e74f2314</v>
+        <v>cc392129-75e3-4205-b7fc-fafceb55b996</v>
       </c>
       <c r="B61" t="str">
-        <v>Ritmos latinos y caribeños</v>
+        <v>Tango (Inter/Avanz)</v>
       </c>
       <c r="C61" t="str">
-        <v>Histórica - Ritmos latinos y caribeños - 2025 - $20.000</v>
+        <v>Histórica - Tango (Inter/Avanz) - 2025 - $30.000</v>
       </c>
       <c r="D61" t="str">
-        <v>20000.00</v>
+        <v>30000.00</v>
       </c>
       <c r="E61" t="str">
-        <v>2025-03-01</v>
+        <v>2025-09-01</v>
       </c>
       <c r="F61" t="str">
-        <v>2025-07-31</v>
+        <v>2025-11-30</v>
       </c>
       <c r="G61" t="str">
-        <v>2025-03 = $20000.00</v>
+        <v>2025-09 = $30000.00</v>
       </c>
       <c r="H61" t="str">
         <v/>
@@ -1990,51 +1991,51 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>71bc486f-8a3d-46bb-a102-838cfef0a1fc</v>
+        <v>cc392129-75e3-4205-b7fc-fafceb55b996</v>
       </c>
       <c r="B62" t="str">
-        <v>S.C Adultos (+18 años)</v>
+        <v>Tango (Inter/Avanz)</v>
       </c>
       <c r="C62" t="str">
-        <v>Histórica - S.C Adultos (+18 años) - 2025 - $15.000</v>
+        <v>Histórica - Tango (Inter/Avanz) - 2026 - $30.000</v>
       </c>
       <c r="D62" t="str">
-        <v>15000.00</v>
+        <v>30000.00</v>
       </c>
       <c r="E62" t="str">
-        <v>2025-02-01</v>
+        <v>2026-03-01</v>
       </c>
       <c r="F62" t="str">
-        <v>2025-02-28</v>
+        <v>2026-07-31</v>
       </c>
       <c r="G62" t="str">
-        <v>2025-02 = $15000.00</v>
+        <v>2026-03 = $30000.00 | 2026-05 = $30000.00</v>
       </c>
       <c r="H62" t="str">
-        <v/>
+        <v>2026-07 ($15000.00)</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>71bc486f-8a3d-46bb-a102-838cfef0a1fc</v>
+        <v>cc392129-75e3-4205-b7fc-fafceb55b996</v>
       </c>
       <c r="B63" t="str">
-        <v>S.C Adultos (+18 años)</v>
+        <v>Tango (Inter/Avanz)</v>
       </c>
       <c r="C63" t="str">
-        <v>Histórica - S.C Adultos (+18 años) - 2025 - $20.000</v>
+        <v>Histórica - Tango (Inter/Avanz) - 2026 - $40.000</v>
       </c>
       <c r="D63" t="str">
-        <v>20000.00</v>
+        <v>40000.00</v>
       </c>
       <c r="E63" t="str">
-        <v>2025-03-01</v>
+        <v>2026-08-01</v>
       </c>
       <c r="F63" t="str">
-        <v>2025-04-30</v>
+        <v>2026-08-31</v>
       </c>
       <c r="G63" t="str">
-        <v>2025-03 = $20000.00</v>
+        <v>2026-08 = $40000.00</v>
       </c>
       <c r="H63" t="str">
         <v/>
@@ -2042,25 +2043,25 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>4b2663bf-5ab4-42e5-865c-2af4da2cf5ff</v>
+        <v>23888530-c53d-4c40-94ee-982518e5d2f6</v>
       </c>
       <c r="B64" t="str">
-        <v>S.C Infantil (6-11 años)</v>
+        <v>Tango Inicial</v>
       </c>
       <c r="C64" t="str">
-        <v>Histórica - S.C Infantil (6-11 años) - 2025 - $15.000</v>
+        <v>Histórica - Tango Inicial - 2026 - $30.000</v>
       </c>
       <c r="D64" t="str">
-        <v>15000.00</v>
+        <v>30000.00</v>
       </c>
       <c r="E64" t="str">
-        <v>2025-02-01</v>
+        <v>2026-03-01</v>
       </c>
       <c r="F64" t="str">
-        <v>2025-02-28</v>
+        <v>2026-03-31</v>
       </c>
       <c r="G64" t="str">
-        <v>2025-02 = $15000.00</v>
+        <v>2026-03 = $30000.00</v>
       </c>
       <c r="H64" t="str">
         <v/>
@@ -2068,25 +2069,25 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>4b2663bf-5ab4-42e5-865c-2af4da2cf5ff</v>
+        <v>da4d15d9-c846-4098-8640-e95fd97c604f</v>
       </c>
       <c r="B65" t="str">
-        <v>S.C Infantil (6-11 años)</v>
+        <v>Teens (8 a 12 años)</v>
       </c>
       <c r="C65" t="str">
-        <v>Histórica - S.C Infantil (6-11 años) - 2025 - $20.000</v>
+        <v>Histórica - Teens (8 a 12 años) - 2025 - $15.000</v>
       </c>
       <c r="D65" t="str">
-        <v>20000.00</v>
+        <v>15000.00</v>
       </c>
       <c r="E65" t="str">
-        <v>2025-03-01</v>
+        <v>2025-02-01</v>
       </c>
       <c r="F65" t="str">
-        <v>2025-04-30</v>
+        <v>2025-02-28</v>
       </c>
       <c r="G65" t="str">
-        <v>2025-03 = $20000.00</v>
+        <v>2025-02 = $15000.00</v>
       </c>
       <c r="H65" t="str">
         <v/>
@@ -2094,25 +2095,25 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>f8a32bf2-9e2a-48b5-9f2e-a8b9da860fb3</v>
+        <v>da4d15d9-c846-4098-8640-e95fd97c604f</v>
       </c>
       <c r="B66" t="str">
-        <v>S.C Juvenil (12-17 años)</v>
+        <v>Teens (8 a 12 años)</v>
       </c>
       <c r="C66" t="str">
-        <v>Histórica - S.C Juvenil (12-17 años) - 2025 - $15.000</v>
+        <v>Histórica - Teens (8 a 12 años) - 2025 - $20.000</v>
       </c>
       <c r="D66" t="str">
-        <v>15000.00</v>
+        <v>20000.00</v>
       </c>
       <c r="E66" t="str">
-        <v>2025-02-01</v>
+        <v>2025-03-01</v>
       </c>
       <c r="F66" t="str">
-        <v>2025-02-28</v>
+        <v>2025-08-31</v>
       </c>
       <c r="G66" t="str">
-        <v>2025-02 = $15000.00</v>
+        <v>2025-03 = $20000.00</v>
       </c>
       <c r="H66" t="str">
         <v/>
@@ -2120,25 +2121,25 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>f8a32bf2-9e2a-48b5-9f2e-a8b9da860fb3</v>
+        <v>da4d15d9-c846-4098-8640-e95fd97c604f</v>
       </c>
       <c r="B67" t="str">
-        <v>S.C Juvenil (12-17 años)</v>
+        <v>Teens (8 a 12 años)</v>
       </c>
       <c r="C67" t="str">
-        <v>Histórica - S.C Juvenil (12-17 años) - 2025 - $20.000</v>
+        <v>Histórica - Teens (8 a 12 años) - 2025 - $30.000</v>
       </c>
       <c r="D67" t="str">
-        <v>20000.00</v>
+        <v>30000.00</v>
       </c>
       <c r="E67" t="str">
-        <v>2025-03-01</v>
+        <v>2025-09-01</v>
       </c>
       <c r="F67" t="str">
-        <v>2025-04-30</v>
+        <v>2025-10-31</v>
       </c>
       <c r="G67" t="str">
-        <v>2025-03 = $20000.00</v>
+        <v>2025-09 = $30000.00</v>
       </c>
       <c r="H67" t="str">
         <v/>
@@ -2146,25 +2147,25 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>dd4b0323-e82f-4b02-89c0-0f8e520033ed</v>
+        <v>da4d15d9-c846-4098-8640-e95fd97c604f</v>
       </c>
       <c r="B68" t="str">
-        <v>Street Int/Avanzado</v>
+        <v>Teens (8 a 12 años)</v>
       </c>
       <c r="C68" t="str">
-        <v>Histórica - Street Int/Avanzado - 2025 - $15.000</v>
+        <v>Histórica - Teens (8 a 12 años) - 2025 - $25.000</v>
       </c>
       <c r="D68" t="str">
-        <v>15000.00</v>
+        <v>25000.00</v>
       </c>
       <c r="E68" t="str">
-        <v>2025-02-01</v>
+        <v>2025-11-01</v>
       </c>
       <c r="F68" t="str">
-        <v>2025-02-28</v>
+        <v>2025-11-30</v>
       </c>
       <c r="G68" t="str">
-        <v>2025-02 = $15000.00</v>
+        <v>2025-11 = $25000.00</v>
       </c>
       <c r="H68" t="str">
         <v/>
@@ -2172,25 +2173,25 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>dd4b0323-e82f-4b02-89c0-0f8e520033ed</v>
+        <v>da4d15d9-c846-4098-8640-e95fd97c604f</v>
       </c>
       <c r="B69" t="str">
-        <v>Street Int/Avanzado</v>
+        <v>Teens (8 a 12 años)</v>
       </c>
       <c r="C69" t="str">
-        <v>Histórica - Street Int/Avanzado - 2025 - $20.000</v>
+        <v>Histórica - Teens (8 a 12 años) - 2026 - $30.000</v>
       </c>
       <c r="D69" t="str">
-        <v>20000.00</v>
+        <v>30000.00</v>
       </c>
       <c r="E69" t="str">
-        <v>2025-03-01</v>
+        <v>2026-01-01</v>
       </c>
       <c r="F69" t="str">
-        <v>2025-04-30</v>
+        <v>2026-01-31</v>
       </c>
       <c r="G69" t="str">
-        <v>2025-03 = $20000.00</v>
+        <v>2026-01 = $30000.00</v>
       </c>
       <c r="H69" t="str">
         <v/>
@@ -2198,25 +2199,25 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>cc392129-75e3-4205-b7fc-fafceb55b996</v>
+        <v>da4d15d9-c846-4098-8640-e95fd97c604f</v>
       </c>
       <c r="B70" t="str">
-        <v>Tango (Inter/Avanz)</v>
+        <v>Teens (8 a 12 años)</v>
       </c>
       <c r="C70" t="str">
-        <v>Histórica - Tango (Inter/Avanz) - 2025 - $15.000</v>
+        <v>Histórica - Teens (8 a 12 años) - 2026 - $15.000</v>
       </c>
       <c r="D70" t="str">
         <v>15000.00</v>
       </c>
       <c r="E70" t="str">
-        <v>2025-02-01</v>
+        <v>2026-02-01</v>
       </c>
       <c r="F70" t="str">
-        <v>2025-02-28</v>
+        <v>2026-02-28</v>
       </c>
       <c r="G70" t="str">
-        <v>2025-02 = $15000.00</v>
+        <v>2026-02 = $15000.00</v>
       </c>
       <c r="H70" t="str">
         <v/>
@@ -2224,51 +2225,51 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>cc392129-75e3-4205-b7fc-fafceb55b996</v>
+        <v>da4d15d9-c846-4098-8640-e95fd97c604f</v>
       </c>
       <c r="B71" t="str">
-        <v>Tango (Inter/Avanz)</v>
+        <v>Teens (8 a 12 años)</v>
       </c>
       <c r="C71" t="str">
-        <v>Histórica - Tango (Inter/Avanz) - 2025 - $20.000</v>
+        <v>Histórica - Teens (8 a 12 años) - 2026 - $30.000</v>
       </c>
       <c r="D71" t="str">
-        <v>20000.00</v>
+        <v>30000.00</v>
       </c>
       <c r="E71" t="str">
-        <v>2025-03-01</v>
+        <v>2026-03-01</v>
       </c>
       <c r="F71" t="str">
-        <v>2025-08-31</v>
+        <v>2026-07-31</v>
       </c>
       <c r="G71" t="str">
-        <v>2025-03 = $20000.00</v>
+        <v>2026-03 = $30000.00 | 2026-05 = $30000.00</v>
       </c>
       <c r="H71" t="str">
-        <v/>
+        <v>2026-07 ($15000.00)</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>cc392129-75e3-4205-b7fc-fafceb55b996</v>
+        <v>da4d15d9-c846-4098-8640-e95fd97c604f</v>
       </c>
       <c r="B72" t="str">
-        <v>Tango (Inter/Avanz)</v>
+        <v>Teens (8 a 12 años)</v>
       </c>
       <c r="C72" t="str">
-        <v>Histórica - Tango (Inter/Avanz) - 2025 - $30.000</v>
+        <v>Histórica - Teens (8 a 12 años) - 2026 - $40.000</v>
       </c>
       <c r="D72" t="str">
-        <v>30000.00</v>
+        <v>40000.00</v>
       </c>
       <c r="E72" t="str">
-        <v>2025-09-01</v>
+        <v>2026-08-01</v>
       </c>
       <c r="F72" t="str">
-        <v>2025-11-30</v>
+        <v>2026-08-31</v>
       </c>
       <c r="G72" t="str">
-        <v>2025-09 = $30000.00</v>
+        <v>2026-08 = $40000.00</v>
       </c>
       <c r="H72" t="str">
         <v/>
@@ -2276,404 +2277,66 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>cc392129-75e3-4205-b7fc-fafceb55b996</v>
+        <v>5e8e8fd7-a08b-4443-8ba0-30ee263ffa1b</v>
       </c>
       <c r="B73" t="str">
-        <v>Tango (Inter/Avanz)</v>
+        <v>Zumba - Profe Joselo</v>
       </c>
       <c r="C73" t="str">
-        <v>Histórica - Tango (Inter/Avanz) - 2026 - $30.000</v>
+        <v>Histórica - Zumba - Profe Joselo - 2026 - $30.000</v>
       </c>
       <c r="D73" t="str">
         <v>30000.00</v>
       </c>
       <c r="E73" t="str">
-        <v>2026-03-01</v>
+        <v>2026-05-01</v>
       </c>
       <c r="F73" t="str">
-        <v>2026-03-31</v>
+        <v>2026-07-31</v>
       </c>
       <c r="G73" t="str">
-        <v>2026-03 = $30000.00</v>
+        <v>2026-05 = $30000.00</v>
       </c>
       <c r="H73" t="str">
-        <v/>
+        <v>2026-07 ($15000.00)</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>cc392129-75e3-4205-b7fc-fafceb55b996</v>
+        <v>5e8e8fd7-a08b-4443-8ba0-30ee263ffa1b</v>
       </c>
       <c r="B74" t="str">
-        <v>Tango (Inter/Avanz)</v>
+        <v>Zumba - Profe Joselo</v>
       </c>
       <c r="C74" t="str">
-        <v>Histórica - Tango (Inter/Avanz) - 2026 - $30.000</v>
+        <v>Histórica - Zumba - Profe Joselo - 2026 - $40.000</v>
       </c>
       <c r="D74" t="str">
-        <v>30000.00</v>
+        <v>40000.00</v>
       </c>
       <c r="E74" t="str">
-        <v>2026-05-01</v>
+        <v>2026-08-01</v>
       </c>
       <c r="F74" t="str">
-        <v>2026-07-31</v>
+        <v>2026-08-31</v>
       </c>
       <c r="G74" t="str">
-        <v>2026-05 = $30000.00</v>
+        <v>2026-08 = $40000.00</v>
       </c>
       <c r="H74" t="str">
-        <v>2026-07 ($15000.00)</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="str">
-        <v>cc392129-75e3-4205-b7fc-fafceb55b996</v>
-      </c>
-      <c r="B75" t="str">
-        <v>Tango (Inter/Avanz)</v>
-      </c>
-      <c r="C75" t="str">
-        <v>Histórica - Tango (Inter/Avanz) - 2026 - $40.000</v>
-      </c>
-      <c r="D75" t="str">
-        <v>40000.00</v>
-      </c>
-      <c r="E75" t="str">
-        <v>2026-08-01</v>
-      </c>
-      <c r="F75" t="str">
-        <v>2026-08-31</v>
-      </c>
-      <c r="G75" t="str">
-        <v>2026-08 = $40000.00</v>
-      </c>
-      <c r="H75" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="str">
-        <v>23888530-c53d-4c40-94ee-982518e5d2f6</v>
-      </c>
-      <c r="B76" t="str">
-        <v>Tango Inicial</v>
-      </c>
-      <c r="C76" t="str">
-        <v>Histórica - Tango Inicial - 2026 - $30.000</v>
-      </c>
-      <c r="D76" t="str">
-        <v>30000.00</v>
-      </c>
-      <c r="E76" t="str">
-        <v>2026-03-01</v>
-      </c>
-      <c r="F76" t="str">
-        <v>2026-03-31</v>
-      </c>
-      <c r="G76" t="str">
-        <v>2026-03 = $30000.00</v>
-      </c>
-      <c r="H76" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="str">
-        <v>da4d15d9-c846-4098-8640-e95fd97c604f</v>
-      </c>
-      <c r="B77" t="str">
-        <v>Teens (8 a 12 años)</v>
-      </c>
-      <c r="C77" t="str">
-        <v>Histórica - Teens (8 a 12 años) - 2025 - $15.000</v>
-      </c>
-      <c r="D77" t="str">
-        <v>15000.00</v>
-      </c>
-      <c r="E77" t="str">
-        <v>2025-02-01</v>
-      </c>
-      <c r="F77" t="str">
-        <v>2025-02-28</v>
-      </c>
-      <c r="G77" t="str">
-        <v>2025-02 = $15000.00</v>
-      </c>
-      <c r="H77" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="str">
-        <v>da4d15d9-c846-4098-8640-e95fd97c604f</v>
-      </c>
-      <c r="B78" t="str">
-        <v>Teens (8 a 12 años)</v>
-      </c>
-      <c r="C78" t="str">
-        <v>Histórica - Teens (8 a 12 años) - 2025 - $20.000</v>
-      </c>
-      <c r="D78" t="str">
-        <v>20000.00</v>
-      </c>
-      <c r="E78" t="str">
-        <v>2025-03-01</v>
-      </c>
-      <c r="F78" t="str">
-        <v>2025-08-31</v>
-      </c>
-      <c r="G78" t="str">
-        <v>2025-03 = $20000.00</v>
-      </c>
-      <c r="H78" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="str">
-        <v>da4d15d9-c846-4098-8640-e95fd97c604f</v>
-      </c>
-      <c r="B79" t="str">
-        <v>Teens (8 a 12 años)</v>
-      </c>
-      <c r="C79" t="str">
-        <v>Histórica - Teens (8 a 12 años) - 2025 - $30.000</v>
-      </c>
-      <c r="D79" t="str">
-        <v>30000.00</v>
-      </c>
-      <c r="E79" t="str">
-        <v>2025-09-01</v>
-      </c>
-      <c r="F79" t="str">
-        <v>2025-10-31</v>
-      </c>
-      <c r="G79" t="str">
-        <v>2025-09 = $30000.00</v>
-      </c>
-      <c r="H79" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="str">
-        <v>da4d15d9-c846-4098-8640-e95fd97c604f</v>
-      </c>
-      <c r="B80" t="str">
-        <v>Teens (8 a 12 años)</v>
-      </c>
-      <c r="C80" t="str">
-        <v>Histórica - Teens (8 a 12 años) - 2025 - $25.000</v>
-      </c>
-      <c r="D80" t="str">
-        <v>25000.00</v>
-      </c>
-      <c r="E80" t="str">
-        <v>2025-11-01</v>
-      </c>
-      <c r="F80" t="str">
-        <v>2025-11-30</v>
-      </c>
-      <c r="G80" t="str">
-        <v>2025-11 = $25000.00</v>
-      </c>
-      <c r="H80" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="str">
-        <v>da4d15d9-c846-4098-8640-e95fd97c604f</v>
-      </c>
-      <c r="B81" t="str">
-        <v>Teens (8 a 12 años)</v>
-      </c>
-      <c r="C81" t="str">
-        <v>Histórica - Teens (8 a 12 años) - 2026 - $30.000</v>
-      </c>
-      <c r="D81" t="str">
-        <v>30000.00</v>
-      </c>
-      <c r="E81" t="str">
-        <v>2026-01-01</v>
-      </c>
-      <c r="F81" t="str">
-        <v>2026-01-31</v>
-      </c>
-      <c r="G81" t="str">
-        <v>2026-01 = $30000.00</v>
-      </c>
-      <c r="H81" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="str">
-        <v>da4d15d9-c846-4098-8640-e95fd97c604f</v>
-      </c>
-      <c r="B82" t="str">
-        <v>Teens (8 a 12 años)</v>
-      </c>
-      <c r="C82" t="str">
-        <v>Histórica - Teens (8 a 12 años) - 2026 - $15.000</v>
-      </c>
-      <c r="D82" t="str">
-        <v>15000.00</v>
-      </c>
-      <c r="E82" t="str">
-        <v>2026-02-01</v>
-      </c>
-      <c r="F82" t="str">
-        <v>2026-02-28</v>
-      </c>
-      <c r="G82" t="str">
-        <v>2026-02 = $15000.00</v>
-      </c>
-      <c r="H82" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="str">
-        <v>da4d15d9-c846-4098-8640-e95fd97c604f</v>
-      </c>
-      <c r="B83" t="str">
-        <v>Teens (8 a 12 años)</v>
-      </c>
-      <c r="C83" t="str">
-        <v>Histórica - Teens (8 a 12 años) - 2026 - $30.000</v>
-      </c>
-      <c r="D83" t="str">
-        <v>30000.00</v>
-      </c>
-      <c r="E83" t="str">
-        <v>2026-03-01</v>
-      </c>
-      <c r="F83" t="str">
-        <v>2026-03-31</v>
-      </c>
-      <c r="G83" t="str">
-        <v>2026-03 = $30000.00</v>
-      </c>
-      <c r="H83" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="str">
-        <v>da4d15d9-c846-4098-8640-e95fd97c604f</v>
-      </c>
-      <c r="B84" t="str">
-        <v>Teens (8 a 12 años)</v>
-      </c>
-      <c r="C84" t="str">
-        <v>Histórica - Teens (8 a 12 años) - 2026 - $30.000</v>
-      </c>
-      <c r="D84" t="str">
-        <v>30000.00</v>
-      </c>
-      <c r="E84" t="str">
-        <v>2026-05-01</v>
-      </c>
-      <c r="F84" t="str">
-        <v>2026-07-31</v>
-      </c>
-      <c r="G84" t="str">
-        <v>2026-05 = $30000.00</v>
-      </c>
-      <c r="H84" t="str">
-        <v>2026-07 ($15000.00)</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="str">
-        <v>da4d15d9-c846-4098-8640-e95fd97c604f</v>
-      </c>
-      <c r="B85" t="str">
-        <v>Teens (8 a 12 años)</v>
-      </c>
-      <c r="C85" t="str">
-        <v>Histórica - Teens (8 a 12 años) - 2026 - $40.000</v>
-      </c>
-      <c r="D85" t="str">
-        <v>40000.00</v>
-      </c>
-      <c r="E85" t="str">
-        <v>2026-08-01</v>
-      </c>
-      <c r="F85" t="str">
-        <v>2026-08-31</v>
-      </c>
-      <c r="G85" t="str">
-        <v>2026-08 = $40000.00</v>
-      </c>
-      <c r="H85" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="str">
-        <v>5e8e8fd7-a08b-4443-8ba0-30ee263ffa1b</v>
-      </c>
-      <c r="B86" t="str">
-        <v>Zumba - Profe Joselo</v>
-      </c>
-      <c r="C86" t="str">
-        <v>Histórica - Zumba - Profe Joselo - 2026 - $30.000</v>
-      </c>
-      <c r="D86" t="str">
-        <v>30000.00</v>
-      </c>
-      <c r="E86" t="str">
-        <v>2026-05-01</v>
-      </c>
-      <c r="F86" t="str">
-        <v>2026-07-31</v>
-      </c>
-      <c r="G86" t="str">
-        <v>2026-05 = $30000.00</v>
-      </c>
-      <c r="H86" t="str">
-        <v>2026-07 ($15000.00)</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="str">
-        <v>5e8e8fd7-a08b-4443-8ba0-30ee263ffa1b</v>
-      </c>
-      <c r="B87" t="str">
-        <v>Zumba - Profe Joselo</v>
-      </c>
-      <c r="C87" t="str">
-        <v>Histórica - Zumba - Profe Joselo - 2026 - $40.000</v>
-      </c>
-      <c r="D87" t="str">
-        <v>40000.00</v>
-      </c>
-      <c r="E87" t="str">
-        <v>2026-08-01</v>
-      </c>
-      <c r="F87" t="str">
-        <v>2026-08-31</v>
-      </c>
-      <c r="G87" t="str">
-        <v>2026-08 = $40000.00</v>
-      </c>
-      <c r="H87" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H87"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H74"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F17"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2746,13 +2409,13 @@
         <v>SOFIA</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-07</v>
+        <v>2025-09</v>
       </c>
       <c r="E4" t="str">
-        <v>15000.00</v>
+        <v>21000.00</v>
       </c>
       <c r="F4" t="str">
-        <v>Medio mes o condición especial</v>
+        <v>Importe particular o condición especial; no representa la tarifa general.</v>
       </c>
     </row>
     <row r="5">
@@ -2760,27 +2423,27 @@
         <v>Clase femenino Sofi</v>
       </c>
       <c r="B5" t="str">
-        <v>Estilo Femenino</v>
+        <v>Coreográfico Femenino</v>
       </c>
       <c r="C5" t="str">
         <v>SOFIA</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-07</v>
+        <v>2026-02</v>
       </c>
       <c r="E5" t="str">
-        <v>15000.00</v>
+        <v>30000.00</v>
       </c>
       <c r="F5" t="str">
-        <v>Medio mes o condición especial</v>
+        <v>La academia confirmó cuota general de $30.000 entre enero y abril de 2026; $15.000 fue un importe especial.</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Infantil (6 a 7 años)</v>
+        <v>Clase femenino Sofi</v>
       </c>
       <c r="B6" t="str">
-        <v>Infantil</v>
+        <v>Coreográfico Femenino</v>
       </c>
       <c r="C6" t="str">
         <v>SOFIA</v>
@@ -2797,73 +2460,73 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Kids 4-5 años</v>
+        <v>Clase femenino Sofi</v>
       </c>
       <c r="B7" t="str">
-        <v>Kids</v>
+        <v>Estilo Femenino</v>
       </c>
       <c r="C7" t="str">
         <v>SOFIA</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-07</v>
+        <v>2025-09</v>
       </c>
       <c r="E7" t="str">
-        <v>15000.00</v>
+        <v>30000.00</v>
       </c>
       <c r="F7" t="str">
-        <v>Medio mes o condición especial</v>
+        <v>Importe particular o condición especial; no representa la tarifa general.</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Mambo en parejas</v>
+        <v>Clase femenino Sofi</v>
       </c>
       <c r="B8" t="str">
-        <v>Mambo en Pareja</v>
+        <v>Estilo Femenino</v>
       </c>
       <c r="C8" t="str">
-        <v>FER</v>
+        <v>SOFIA</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-07</v>
+        <v>2026-02</v>
       </c>
       <c r="E8" t="str">
         <v>15000.00</v>
       </c>
       <c r="F8" t="str">
-        <v>Medio mes o condición especial</v>
+        <v>La academia confirmó cuota general de $30.000 entre enero y abril de 2026; $15.000 fue un importe especial.</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Bachata y Salsa Inicial</v>
+        <v>Clase femenino Sofi</v>
       </c>
       <c r="B9" t="str">
-        <v>Salsa Inicial / Siesta</v>
+        <v>Estilo Femenino</v>
       </c>
       <c r="C9" t="str">
-        <v>JAVI</v>
+        <v>SOFIA</v>
       </c>
       <c r="D9" t="str">
-        <v>2025-09</v>
+        <v>2026-07</v>
       </c>
       <c r="E9" t="str">
-        <v>7500.00</v>
+        <v>15000.00</v>
       </c>
       <c r="F9" t="str">
-        <v>Condición especial definida por el profesor</v>
+        <v>Medio mes o condición especial</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Tango (Inter/Avanz)</v>
+        <v>Infantil (6 a 7 años)</v>
       </c>
       <c r="B10" t="str">
-        <v>Tango Avanzado/Intermedio</v>
+        <v>Infantil</v>
       </c>
       <c r="C10" t="str">
-        <v>ROBERTO</v>
+        <v>SOFIA</v>
       </c>
       <c r="D10" t="str">
         <v>2026-07</v>
@@ -2877,10 +2540,10 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Teens (8 a 12 años)</v>
+        <v>Kids 4-5 años</v>
       </c>
       <c r="B11" t="str">
-        <v>Teens</v>
+        <v>Kids</v>
       </c>
       <c r="C11" t="str">
         <v>SOFIA</v>
@@ -2897,13 +2560,13 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Zumba - Profe Joselo</v>
+        <v>Mambo en parejas</v>
       </c>
       <c r="B12" t="str">
-        <v>Zumba</v>
+        <v>Mambo en Pareja</v>
       </c>
       <c r="C12" t="str">
-        <v>JOSELO</v>
+        <v>FER</v>
       </c>
       <c r="D12" t="str">
         <v>2026-07</v>
@@ -2915,16 +2578,116 @@
         <v>Medio mes o condición especial</v>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>Bachata y Salsa Inicial</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Salsa Inicial / Siesta</v>
+      </c>
+      <c r="C13" t="str">
+        <v>JAVI</v>
+      </c>
+      <c r="D13" t="str">
+        <v>2025-09</v>
+      </c>
+      <c r="E13" t="str">
+        <v>7500.00</v>
+      </c>
+      <c r="F13" t="str">
+        <v>Condición especial definida por el profesor</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>Bachata y Salsa Inicial</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Salsa Inicial / Siesta</v>
+      </c>
+      <c r="C14" t="str">
+        <v>JAVI</v>
+      </c>
+      <c r="D14" t="str">
+        <v>2025-10</v>
+      </c>
+      <c r="E14" t="str">
+        <v>25000.00</v>
+      </c>
+      <c r="F14" t="str">
+        <v>La academia confirmó tarifa general de $30.000 entre septiembre y noviembre de 2025; $25.000 fue un importe especial.</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>Tango (Inter/Avanz)</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Tango Avanzado/Intermedio</v>
+      </c>
+      <c r="C15" t="str">
+        <v>ROBERTO</v>
+      </c>
+      <c r="D15" t="str">
+        <v>2026-07</v>
+      </c>
+      <c r="E15" t="str">
+        <v>15000.00</v>
+      </c>
+      <c r="F15" t="str">
+        <v>Medio mes o condición especial</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>Teens (8 a 12 años)</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Teens</v>
+      </c>
+      <c r="C16" t="str">
+        <v>SOFIA</v>
+      </c>
+      <c r="D16" t="str">
+        <v>2026-07</v>
+      </c>
+      <c r="E16" t="str">
+        <v>15000.00</v>
+      </c>
+      <c r="F16" t="str">
+        <v>Medio mes o condición especial</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>Zumba - Profe Joselo</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Zumba</v>
+      </c>
+      <c r="C17" t="str">
+        <v>JOSELO</v>
+      </c>
+      <c r="D17" t="str">
+        <v>2026-07</v>
+      </c>
+      <c r="E17" t="str">
+        <v>15000.00</v>
+      </c>
+      <c r="F17" t="str">
+        <v>Medio mes o condición especial</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F12"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F17"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2948,16 +2711,16 @@
         <v>UNEXPLAINED_GAP</v>
       </c>
       <c r="B2" t="str">
-        <v>Árabe infantil</v>
+        <v>Clase femenino Sofi</v>
       </c>
       <c r="C2" t="str">
-        <v>2025-07-31</v>
+        <v>2025-08-31</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-08-01</v>
+        <v>2025-11-01</v>
       </c>
       <c r="E2" t="str">
-        <v>2025-08, 2025-09, 2025-10, 2025-11, 2025-12, 2026-01, 2026-02, 2026-03, 2026-04, 2026-05, 2026-06, 2026-07</v>
+        <v>2025-10</v>
       </c>
     </row>
     <row r="3">
@@ -2965,16 +2728,16 @@
         <v>UNEXPLAINED_GAP</v>
       </c>
       <c r="B3" t="str">
-        <v>Bachata y Salsa Inicial</v>
+        <v>Clase femenino Sofi</v>
       </c>
       <c r="C3" t="str">
-        <v>2025-07-31</v>
+        <v>2025-11-30</v>
       </c>
       <c r="D3" t="str">
-        <v>2025-09-01</v>
+        <v>2026-03-01</v>
       </c>
       <c r="E3" t="str">
-        <v>2025-08</v>
+        <v>2026-01</v>
       </c>
     </row>
     <row r="4">
@@ -2982,16 +2745,16 @@
         <v>UNEXPLAINED_GAP</v>
       </c>
       <c r="B4" t="str">
-        <v>Bachata y Salsa Inicial</v>
+        <v>Clase LT - A.Frank</v>
       </c>
       <c r="C4" t="str">
-        <v>2025-10-31</v>
+        <v>2026-06-30</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-05-01</v>
+        <v>2026-08-01</v>
       </c>
       <c r="E4" t="str">
-        <v>2025-11, 2025-12, 2026-01, 2026-02, 2026-03, 2026-04</v>
+        <v>2026-07</v>
       </c>
     </row>
     <row r="5">
@@ -2999,266 +2762,117 @@
         <v>UNEXPLAINED_GAP</v>
       </c>
       <c r="B5" t="str">
-        <v>Clase femenino Sofi</v>
+        <v>Tango (Inter/Avanz)</v>
       </c>
       <c r="C5" t="str">
         <v>2025-11-30</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-02-01</v>
+        <v>2026-03-01</v>
       </c>
       <c r="E5" t="str">
-        <v>2025-12, 2026-01</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>UNEXPLAINED_GAP</v>
-      </c>
-      <c r="B6" t="str">
-        <v>Clase femenino Sofi</v>
-      </c>
-      <c r="C6" t="str">
-        <v>2026-03-31</v>
-      </c>
-      <c r="D6" t="str">
-        <v>2026-05-01</v>
-      </c>
-      <c r="E6" t="str">
-        <v>2026-04</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>UNEXPLAINED_GAP</v>
-      </c>
-      <c r="B7" t="str">
-        <v>Grupo C. - A.Frank</v>
-      </c>
-      <c r="C7" t="str">
-        <v>2026-03-31</v>
-      </c>
-      <c r="D7" t="str">
-        <v>2026-05-01</v>
-      </c>
-      <c r="E7" t="str">
-        <v>2026-04</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>UNEXPLAINED_GAP</v>
-      </c>
-      <c r="B8" t="str">
-        <v>Infantil (6 a 7 años)</v>
-      </c>
-      <c r="C8" t="str">
-        <v>2025-11-30</v>
-      </c>
-      <c r="D8" t="str">
-        <v>2026-01-01</v>
-      </c>
-      <c r="E8" t="str">
-        <v>2025-12</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>UNEXPLAINED_GAP</v>
-      </c>
-      <c r="B9" t="str">
-        <v>Infantil (6 a 7 años)</v>
-      </c>
-      <c r="C9" t="str">
-        <v>2026-03-31</v>
-      </c>
-      <c r="D9" t="str">
-        <v>2026-05-01</v>
-      </c>
-      <c r="E9" t="str">
-        <v>2026-04</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>UNEXPLAINED_GAP</v>
-      </c>
-      <c r="B10" t="str">
-        <v>Kids 4-5 años</v>
-      </c>
-      <c r="C10" t="str">
-        <v>2025-07-31</v>
-      </c>
-      <c r="D10" t="str">
-        <v>2026-01-01</v>
-      </c>
-      <c r="E10" t="str">
-        <v>2025-08, 2025-09, 2025-10, 2025-11, 2025-12</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>UNEXPLAINED_GAP</v>
-      </c>
-      <c r="B11" t="str">
-        <v>Kids 4-5 años</v>
-      </c>
-      <c r="C11" t="str">
-        <v>2026-03-31</v>
-      </c>
-      <c r="D11" t="str">
-        <v>2026-05-01</v>
-      </c>
-      <c r="E11" t="str">
-        <v>2026-04</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>UNEXPLAINED_GAP</v>
-      </c>
-      <c r="B12" t="str">
-        <v>Clase LT - A.Frank</v>
-      </c>
-      <c r="C12" t="str">
-        <v>2025-11-30</v>
-      </c>
-      <c r="D12" t="str">
-        <v>2026-01-01</v>
-      </c>
-      <c r="E12" t="str">
-        <v>2025-12</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>UNEXPLAINED_GAP</v>
-      </c>
-      <c r="B13" t="str">
-        <v>Clase LT - A.Frank</v>
-      </c>
-      <c r="C13" t="str">
-        <v>2026-03-31</v>
-      </c>
-      <c r="D13" t="str">
-        <v>2026-05-01</v>
-      </c>
-      <c r="E13" t="str">
-        <v>2026-04</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>UNEXPLAINED_GAP</v>
-      </c>
-      <c r="B14" t="str">
-        <v>Clase LT - A.Frank</v>
-      </c>
-      <c r="C14" t="str">
-        <v>2026-06-30</v>
-      </c>
-      <c r="D14" t="str">
-        <v>2026-08-01</v>
-      </c>
-      <c r="E14" t="str">
-        <v>2026-07</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>UNEXPLAINED_GAP</v>
-      </c>
-      <c r="B15" t="str">
-        <v>Mambo en parejas</v>
-      </c>
-      <c r="C15" t="str">
-        <v>2026-03-31</v>
-      </c>
-      <c r="D15" t="str">
-        <v>2026-05-01</v>
-      </c>
-      <c r="E15" t="str">
-        <v>2026-04</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>UNEXPLAINED_GAP</v>
-      </c>
-      <c r="B16" t="str">
-        <v>Tango (Inter/Avanz)</v>
-      </c>
-      <c r="C16" t="str">
-        <v>2025-11-30</v>
-      </c>
-      <c r="D16" t="str">
-        <v>2026-03-01</v>
-      </c>
-      <c r="E16" t="str">
-        <v>2025-12, 2026-01, 2026-02</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>UNEXPLAINED_GAP</v>
-      </c>
-      <c r="B17" t="str">
-        <v>Tango (Inter/Avanz)</v>
-      </c>
-      <c r="C17" t="str">
-        <v>2026-03-31</v>
-      </c>
-      <c r="D17" t="str">
-        <v>2026-05-01</v>
-      </c>
-      <c r="E17" t="str">
-        <v>2026-04</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>UNEXPLAINED_GAP</v>
-      </c>
-      <c r="B18" t="str">
-        <v>Teens (8 a 12 años)</v>
-      </c>
-      <c r="C18" t="str">
-        <v>2025-11-30</v>
-      </c>
-      <c r="D18" t="str">
-        <v>2026-01-01</v>
-      </c>
-      <c r="E18" t="str">
-        <v>2025-12</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>UNEXPLAINED_GAP</v>
-      </c>
-      <c r="B19" t="str">
-        <v>Teens (8 a 12 años)</v>
-      </c>
-      <c r="C19" t="str">
-        <v>2026-03-31</v>
-      </c>
-      <c r="D19" t="str">
-        <v>2026-05-01</v>
-      </c>
-      <c r="E19" t="str">
-        <v>2026-04</v>
+        <v>2026-01, 2026-02</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E19"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E5"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:H3"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tipo</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Clase</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Importe 1</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Desde 1</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Hasta 1</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Importe 2</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Desde 2</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Hasta 2</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>OVERLAPPING_DIFFERENT_AMOUNTS</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Clase femenino Sofi</v>
+      </c>
+      <c r="C2" t="str">
+        <v>7500.00</v>
+      </c>
+      <c r="D2" t="str">
+        <v>2025-02-01</v>
+      </c>
+      <c r="E2" t="str">
+        <v>2025-02-28</v>
+      </c>
+      <c r="F2" t="str">
+        <v>15000.00</v>
+      </c>
+      <c r="G2" t="str">
+        <v>2025-02-01</v>
+      </c>
+      <c r="H2" t="str">
+        <v>2025-03-31</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>OVERLAPPING_DIFFERENT_AMOUNTS</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Clase femenino Sofi</v>
+      </c>
+      <c r="C3" t="str">
+        <v>15000.00</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2025-02-01</v>
+      </c>
+      <c r="E3" t="str">
+        <v>2025-03-31</v>
+      </c>
+      <c r="F3" t="str">
+        <v>20000.00</v>
+      </c>
+      <c r="G3" t="str">
+        <v>2025-03-01</v>
+      </c>
+      <c r="H3" t="str">
+        <v>2025-08-31</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:H3"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B9"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3281,7 +2895,7 @@
         <v>Registros OK</v>
       </c>
       <c r="B3">
-        <v>86</v>
+        <v>81</v>
       </c>
     </row>
     <row r="4">
@@ -3289,7 +2903,7 @@
         <v>Importes especiales</v>
       </c>
       <c r="B4">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5">
@@ -3305,7 +2919,7 @@
         <v>Tarifas consolidadas</v>
       </c>
       <c r="B6">
-        <v>86</v>
+        <v>73</v>
       </c>
     </row>
     <row r="7">
@@ -3313,7 +2927,7 @@
         <v>Períodos especiales puenteados</v>
       </c>
       <c r="B7">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
@@ -3321,12 +2935,20 @@
         <v>Huecos sin explicar</v>
       </c>
       <c r="B8">
-        <v>18</v>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>Solapamientos conflictivos</v>
+      </c>
+      <c r="B9">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B8"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B9"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/exports/historical-tariffs-ready.xlsx
+++ b/exports/historical-tariffs-ready.xlsx
@@ -801,10 +801,10 @@
         <v>Clase femenino Sofi</v>
       </c>
       <c r="C16" t="str">
-        <v>Histórica - Clase femenino Sofi - 2025 - $7.500</v>
+        <v>Histórica - Clase femenino Sofi - 2025 - $15.000</v>
       </c>
       <c r="D16" t="str">
-        <v>7500.00</v>
+        <v>15000.00</v>
       </c>
       <c r="E16" t="str">
         <v>2025-02-01</v>
@@ -813,7 +813,7 @@
         <v>2025-02-28</v>
       </c>
       <c r="G16" t="str">
-        <v>2025-02 = $7500.00</v>
+        <v>2025-02 = $15000.00</v>
       </c>
       <c r="H16" t="str">
         <v/>
@@ -827,22 +827,22 @@
         <v>Clase femenino Sofi</v>
       </c>
       <c r="C17" t="str">
-        <v>Histórica - Clase femenino Sofi - 2025 - $15.000</v>
+        <v>Histórica - Clase femenino Sofi - 2025 - $20.000</v>
       </c>
       <c r="D17" t="str">
-        <v>15000.00</v>
+        <v>20000.00</v>
       </c>
       <c r="E17" t="str">
-        <v>2025-02-01</v>
+        <v>2025-03-01</v>
       </c>
       <c r="F17" t="str">
-        <v>2025-03-31</v>
+        <v>2025-09-30</v>
       </c>
       <c r="G17" t="str">
-        <v>2025-02 = $15000.00</v>
+        <v>2025-03 = $20000.00 | 2025-04 = $20000.00</v>
       </c>
       <c r="H17" t="str">
-        <v/>
+        <v>2025-09 ($30000.00)</v>
       </c>
     </row>
     <row r="18">
@@ -853,22 +853,22 @@
         <v>Clase femenino Sofi</v>
       </c>
       <c r="C18" t="str">
-        <v>Histórica - Clase femenino Sofi - 2025 - $20.000</v>
+        <v>Histórica - Clase femenino Sofi - 2025 - $30.000</v>
       </c>
       <c r="D18" t="str">
-        <v>20000.00</v>
+        <v>30000.00</v>
       </c>
       <c r="E18" t="str">
-        <v>2025-03-01</v>
+        <v>2025-10-01</v>
       </c>
       <c r="F18" t="str">
-        <v>2025-09-30</v>
+        <v>2025-10-31</v>
       </c>
       <c r="G18" t="str">
-        <v>2025-03 = $20000.00 | 2025-04 = $20000.00</v>
+        <v/>
       </c>
       <c r="H18" t="str">
-        <v>2025-09 ($30000.00)</v>
+        <v/>
       </c>
     </row>
     <row r="19">
@@ -2336,7 +2336,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F18"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2469,13 +2469,13 @@
         <v>SOFIA</v>
       </c>
       <c r="D7" t="str">
-        <v>2025-09</v>
+        <v>2025-02</v>
       </c>
       <c r="E7" t="str">
-        <v>30000.00</v>
+        <v>7500.00</v>
       </c>
       <c r="F7" t="str">
-        <v>Importe particular o condición especial; no representa la tarifa general.</v>
+        <v>La academia confirmó que la cuota general de febrero de 2025 era $15.000; $7.500 correspondía a una condición especial.</v>
       </c>
     </row>
     <row r="8">
@@ -2489,13 +2489,13 @@
         <v>SOFIA</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-02</v>
+        <v>2025-09</v>
       </c>
       <c r="E8" t="str">
-        <v>15000.00</v>
+        <v>30000.00</v>
       </c>
       <c r="F8" t="str">
-        <v>La academia confirmó cuota general de $30.000 entre enero y abril de 2026; $15.000 fue un importe especial.</v>
+        <v>Importe particular o condición especial; no representa la tarifa general.</v>
       </c>
     </row>
     <row r="9">
@@ -2509,21 +2509,21 @@
         <v>SOFIA</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-07</v>
+        <v>2026-02</v>
       </c>
       <c r="E9" t="str">
         <v>15000.00</v>
       </c>
       <c r="F9" t="str">
-        <v>Medio mes o condición especial</v>
+        <v>La academia confirmó cuota general de $30.000 entre enero y abril de 2026; $15.000 fue un importe especial.</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Infantil (6 a 7 años)</v>
+        <v>Clase femenino Sofi</v>
       </c>
       <c r="B10" t="str">
-        <v>Infantil</v>
+        <v>Estilo Femenino</v>
       </c>
       <c r="C10" t="str">
         <v>SOFIA</v>
@@ -2540,10 +2540,10 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Kids 4-5 años</v>
+        <v>Infantil (6 a 7 años)</v>
       </c>
       <c r="B11" t="str">
-        <v>Kids</v>
+        <v>Infantil</v>
       </c>
       <c r="C11" t="str">
         <v>SOFIA</v>
@@ -2560,13 +2560,13 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Mambo en parejas</v>
+        <v>Kids 4-5 años</v>
       </c>
       <c r="B12" t="str">
-        <v>Mambo en Pareja</v>
+        <v>Kids</v>
       </c>
       <c r="C12" t="str">
-        <v>FER</v>
+        <v>SOFIA</v>
       </c>
       <c r="D12" t="str">
         <v>2026-07</v>
@@ -2580,22 +2580,22 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Bachata y Salsa Inicial</v>
+        <v>Mambo en parejas</v>
       </c>
       <c r="B13" t="str">
-        <v>Salsa Inicial / Siesta</v>
+        <v>Mambo en Pareja</v>
       </c>
       <c r="C13" t="str">
-        <v>JAVI</v>
+        <v>FER</v>
       </c>
       <c r="D13" t="str">
-        <v>2025-09</v>
+        <v>2026-07</v>
       </c>
       <c r="E13" t="str">
-        <v>7500.00</v>
+        <v>15000.00</v>
       </c>
       <c r="F13" t="str">
-        <v>Condición especial definida por el profesor</v>
+        <v>Medio mes o condición especial</v>
       </c>
     </row>
     <row r="14">
@@ -2609,44 +2609,44 @@
         <v>JAVI</v>
       </c>
       <c r="D14" t="str">
-        <v>2025-10</v>
+        <v>2025-09</v>
       </c>
       <c r="E14" t="str">
-        <v>25000.00</v>
+        <v>7500.00</v>
       </c>
       <c r="F14" t="str">
-        <v>La academia confirmó tarifa general de $30.000 entre septiembre y noviembre de 2025; $25.000 fue un importe especial.</v>
+        <v>Condición especial definida por el profesor</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Tango (Inter/Avanz)</v>
+        <v>Bachata y Salsa Inicial</v>
       </c>
       <c r="B15" t="str">
-        <v>Tango Avanzado/Intermedio</v>
+        <v>Salsa Inicial / Siesta</v>
       </c>
       <c r="C15" t="str">
-        <v>ROBERTO</v>
+        <v>JAVI</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-07</v>
+        <v>2025-10</v>
       </c>
       <c r="E15" t="str">
-        <v>15000.00</v>
+        <v>25000.00</v>
       </c>
       <c r="F15" t="str">
-        <v>Medio mes o condición especial</v>
+        <v>La academia confirmó tarifa general de $30.000 entre septiembre y noviembre de 2025; $25.000 fue un importe especial.</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Teens (8 a 12 años)</v>
+        <v>Tango (Inter/Avanz)</v>
       </c>
       <c r="B16" t="str">
-        <v>Teens</v>
+        <v>Tango Avanzado/Intermedio</v>
       </c>
       <c r="C16" t="str">
-        <v>SOFIA</v>
+        <v>ROBERTO</v>
       </c>
       <c r="D16" t="str">
         <v>2026-07</v>
@@ -2660,13 +2660,13 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Zumba - Profe Joselo</v>
+        <v>Teens (8 a 12 años)</v>
       </c>
       <c r="B17" t="str">
-        <v>Zumba</v>
+        <v>Teens</v>
       </c>
       <c r="C17" t="str">
-        <v>JOSELO</v>
+        <v>SOFIA</v>
       </c>
       <c r="D17" t="str">
         <v>2026-07</v>
@@ -2678,194 +2678,49 @@
         <v>Medio mes o condición especial</v>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>Zumba - Profe Joselo</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Zumba</v>
+      </c>
+      <c r="C18" t="str">
+        <v>JOSELO</v>
+      </c>
+      <c r="D18" t="str">
+        <v>2026-07</v>
+      </c>
+      <c r="E18" t="str">
+        <v>15000.00</v>
+      </c>
+      <c r="F18" t="str">
+        <v>Medio mes o condición especial</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F17"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F18"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E5"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tipo</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Clase</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Vigencia anterior hasta</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Próxima vigencia desde</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Meses faltantes</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>UNEXPLAINED_GAP</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Clase femenino Sofi</v>
-      </c>
-      <c r="C2" t="str">
-        <v>2025-08-31</v>
-      </c>
-      <c r="D2" t="str">
-        <v>2025-11-01</v>
-      </c>
-      <c r="E2" t="str">
-        <v>2025-10</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>UNEXPLAINED_GAP</v>
-      </c>
-      <c r="B3" t="str">
-        <v>Clase femenino Sofi</v>
-      </c>
-      <c r="C3" t="str">
-        <v>2025-11-30</v>
-      </c>
-      <c r="D3" t="str">
-        <v>2026-03-01</v>
-      </c>
-      <c r="E3" t="str">
-        <v>2026-01</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>UNEXPLAINED_GAP</v>
-      </c>
-      <c r="B4" t="str">
-        <v>Clase LT - A.Frank</v>
-      </c>
-      <c r="C4" t="str">
-        <v>2026-06-30</v>
-      </c>
-      <c r="D4" t="str">
-        <v>2026-08-01</v>
-      </c>
-      <c r="E4" t="str">
-        <v>2026-07</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>UNEXPLAINED_GAP</v>
-      </c>
-      <c r="B5" t="str">
-        <v>Tango (Inter/Avanz)</v>
-      </c>
-      <c r="C5" t="str">
-        <v>2025-11-30</v>
-      </c>
-      <c r="D5" t="str">
-        <v>2026-03-01</v>
-      </c>
-      <c r="E5" t="str">
-        <v>2026-01, 2026-02</v>
-      </c>
-    </row>
-  </sheetData>
+  <dimension ref="A1"/>
+  <sheetData/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H3"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tipo</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Clase</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Importe 1</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Desde 1</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Hasta 1</v>
-      </c>
-      <c r="F1" t="str">
-        <v>Importe 2</v>
-      </c>
-      <c r="G1" t="str">
-        <v>Desde 2</v>
-      </c>
-      <c r="H1" t="str">
-        <v>Hasta 2</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>OVERLAPPING_DIFFERENT_AMOUNTS</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Clase femenino Sofi</v>
-      </c>
-      <c r="C2" t="str">
-        <v>7500.00</v>
-      </c>
-      <c r="D2" t="str">
-        <v>2025-02-01</v>
-      </c>
-      <c r="E2" t="str">
-        <v>2025-02-28</v>
-      </c>
-      <c r="F2" t="str">
-        <v>15000.00</v>
-      </c>
-      <c r="G2" t="str">
-        <v>2025-02-01</v>
-      </c>
-      <c r="H2" t="str">
-        <v>2025-03-31</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>OVERLAPPING_DIFFERENT_AMOUNTS</v>
-      </c>
-      <c r="B3" t="str">
-        <v>Clase femenino Sofi</v>
-      </c>
-      <c r="C3" t="str">
-        <v>15000.00</v>
-      </c>
-      <c r="D3" t="str">
-        <v>2025-02-01</v>
-      </c>
-      <c r="E3" t="str">
-        <v>2025-03-31</v>
-      </c>
-      <c r="F3" t="str">
-        <v>20000.00</v>
-      </c>
-      <c r="G3" t="str">
-        <v>2025-03-01</v>
-      </c>
-      <c r="H3" t="str">
-        <v>2025-08-31</v>
-      </c>
-    </row>
-  </sheetData>
+  <dimension ref="A1"/>
+  <sheetData/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2895,7 +2750,7 @@
         <v>Registros OK</v>
       </c>
       <c r="B3">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="4">
@@ -2903,7 +2758,7 @@
         <v>Importes especiales</v>
       </c>
       <c r="B4">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5">
@@ -2935,7 +2790,7 @@
         <v>Huecos sin explicar</v>
       </c>
       <c r="B8">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -2943,7 +2798,7 @@
         <v>Solapamientos conflictivos</v>
       </c>
       <c r="B9">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/exports/historical-tariffs-ready.xlsx
+++ b/exports/historical-tariffs-ready.xlsx
@@ -401,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H74"/>
+  <dimension ref="A1:H94"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1460,10 +1460,10 @@
         <v>2025-03-01</v>
       </c>
       <c r="F41" t="str">
-        <v>2025-07-31</v>
+        <v>2025-08-31</v>
       </c>
       <c r="G41" t="str">
-        <v>2025-03 = $20000.00</v>
+        <v>2025-03 = $20000.00 | 2025-08 = $20000.00</v>
       </c>
       <c r="H41" t="str">
         <v/>
@@ -1471,25 +1471,25 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>a12f5acf-4754-479a-853c-15926c2dac92</v>
+        <v>06f93e1a-5cc0-4741-8ad6-813745ea389d</v>
       </c>
       <c r="B42" t="str">
-        <v>Ladys Tango - Gabriela P.</v>
+        <v>Ladys Kizz</v>
       </c>
       <c r="C42" t="str">
-        <v>Histórica - Ladys Tango - Gabriela P. - 2025 - $7.500</v>
+        <v>Histórica - Ladys Kizz - 2025 - $30.000</v>
       </c>
       <c r="D42" t="str">
-        <v>7500.00</v>
+        <v>30000.00</v>
       </c>
       <c r="E42" t="str">
-        <v>2025-02-01</v>
+        <v>2025-09-01</v>
       </c>
       <c r="F42" t="str">
-        <v>2025-02-28</v>
+        <v>2025-11-30</v>
       </c>
       <c r="G42" t="str">
-        <v>2025-02 = $7500.00</v>
+        <v>2025-09 = $30000.00</v>
       </c>
       <c r="H42" t="str">
         <v/>
@@ -1497,25 +1497,25 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>a12f5acf-4754-479a-853c-15926c2dac92</v>
+        <v>06f93e1a-5cc0-4741-8ad6-813745ea389d</v>
       </c>
       <c r="B43" t="str">
-        <v>Ladys Tango - Gabriela P.</v>
+        <v>Ladys Kizz</v>
       </c>
       <c r="C43" t="str">
-        <v>Histórica - Ladys Tango - Gabriela P. - 2025 - $10.000</v>
+        <v>Histórica - Ladys Kizz - 2026 - $30.000</v>
       </c>
       <c r="D43" t="str">
-        <v>10000.00</v>
+        <v>30000.00</v>
       </c>
       <c r="E43" t="str">
-        <v>2025-03-01</v>
+        <v>2026-01-01</v>
       </c>
       <c r="F43" t="str">
-        <v>2025-04-30</v>
+        <v>2026-06-30</v>
       </c>
       <c r="G43" t="str">
-        <v>2025-03 = $10000.00</v>
+        <v>2026-01 = $30000.00</v>
       </c>
       <c r="H43" t="str">
         <v/>
@@ -1523,25 +1523,25 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>a12f5acf-4754-479a-853c-15926c2dac92</v>
+        <v>06f93e1a-5cc0-4741-8ad6-813745ea389d</v>
       </c>
       <c r="B44" t="str">
-        <v>Ladys Tango - Gabriela P.</v>
+        <v>Ladys Kizz</v>
       </c>
       <c r="C44" t="str">
-        <v>Histórica - Ladys Tango - Gabriela P. - 2025 - $11.000</v>
+        <v>Histórica - Ladys Kizz - 2026 - $15.000</v>
       </c>
       <c r="D44" t="str">
-        <v>11000.00</v>
+        <v>15000.00</v>
       </c>
       <c r="E44" t="str">
-        <v>2025-05-01</v>
+        <v>2026-07-01</v>
       </c>
       <c r="F44" t="str">
-        <v>2025-06-30</v>
+        <v>2026-07-31</v>
       </c>
       <c r="G44" t="str">
-        <v>2025-05 = $11000.00</v>
+        <v>2026-07 = $15000.00</v>
       </c>
       <c r="H44" t="str">
         <v/>
@@ -1549,25 +1549,25 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>a12f5acf-4754-479a-853c-15926c2dac92</v>
+        <v>06f93e1a-5cc0-4741-8ad6-813745ea389d</v>
       </c>
       <c r="B45" t="str">
-        <v>Ladys Tango - Gabriela P.</v>
+        <v>Ladys Kizz</v>
       </c>
       <c r="C45" t="str">
-        <v>Histórica - Ladys Tango - Gabriela P. - 2025 - $20.000</v>
+        <v>Histórica - Ladys Kizz - 2026 - $40.000</v>
       </c>
       <c r="D45" t="str">
-        <v>20000.00</v>
+        <v>40000.00</v>
       </c>
       <c r="E45" t="str">
-        <v>2025-07-01</v>
+        <v>2026-08-01</v>
       </c>
       <c r="F45" t="str">
-        <v>2025-07-31</v>
+        <v>2026-08-31</v>
       </c>
       <c r="G45" t="str">
-        <v>2025-07 = $20000.00</v>
+        <v>2026-08 = $40000.00</v>
       </c>
       <c r="H45" t="str">
         <v/>
@@ -1575,25 +1575,25 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>b96017bd-9ee1-4bde-ad35-ad961a78e5f5</v>
+        <v>a12f5acf-4754-479a-853c-15926c2dac92</v>
       </c>
       <c r="B46" t="str">
-        <v>Mambo en parejas</v>
+        <v>Ladys Tango - Gabriela P.</v>
       </c>
       <c r="C46" t="str">
-        <v>Histórica - Mambo en parejas - 2026 - $15.000</v>
+        <v>Histórica - Ladys Tango - Gabriela P. - 2025 - $7.500</v>
       </c>
       <c r="D46" t="str">
-        <v>15000.00</v>
+        <v>7500.00</v>
       </c>
       <c r="E46" t="str">
-        <v>2026-02-01</v>
+        <v>2025-02-01</v>
       </c>
       <c r="F46" t="str">
-        <v>2026-02-28</v>
+        <v>2025-02-28</v>
       </c>
       <c r="G46" t="str">
-        <v>2026-02 = $15000.00</v>
+        <v>2025-02 = $7500.00</v>
       </c>
       <c r="H46" t="str">
         <v/>
@@ -1601,51 +1601,51 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>b96017bd-9ee1-4bde-ad35-ad961a78e5f5</v>
+        <v>a12f5acf-4754-479a-853c-15926c2dac92</v>
       </c>
       <c r="B47" t="str">
-        <v>Mambo en parejas</v>
+        <v>Ladys Tango - Gabriela P.</v>
       </c>
       <c r="C47" t="str">
-        <v>Histórica - Mambo en parejas - 2026 - $30.000</v>
+        <v>Histórica - Ladys Tango - Gabriela P. - 2025 - $10.000</v>
       </c>
       <c r="D47" t="str">
-        <v>30000.00</v>
+        <v>10000.00</v>
       </c>
       <c r="E47" t="str">
-        <v>2026-03-01</v>
+        <v>2025-03-01</v>
       </c>
       <c r="F47" t="str">
-        <v>2026-07-31</v>
+        <v>2025-04-30</v>
       </c>
       <c r="G47" t="str">
-        <v>2026-03 = $30000.00 | 2026-05 = $30000.00</v>
+        <v>2025-03 = $10000.00</v>
       </c>
       <c r="H47" t="str">
-        <v>2026-07 ($15000.00)</v>
+        <v/>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>b96017bd-9ee1-4bde-ad35-ad961a78e5f5</v>
+        <v>a12f5acf-4754-479a-853c-15926c2dac92</v>
       </c>
       <c r="B48" t="str">
-        <v>Mambo en parejas</v>
+        <v>Ladys Tango - Gabriela P.</v>
       </c>
       <c r="C48" t="str">
-        <v>Histórica - Mambo en parejas - 2026 - $40.000</v>
+        <v>Histórica - Ladys Tango - Gabriela P. - 2025 - $11.000</v>
       </c>
       <c r="D48" t="str">
-        <v>40000.00</v>
+        <v>11000.00</v>
       </c>
       <c r="E48" t="str">
-        <v>2026-08-01</v>
+        <v>2025-05-01</v>
       </c>
       <c r="F48" t="str">
-        <v>2026-08-31</v>
+        <v>2025-06-30</v>
       </c>
       <c r="G48" t="str">
-        <v>2026-08 = $40000.00</v>
+        <v>2025-05 = $11000.00</v>
       </c>
       <c r="H48" t="str">
         <v/>
@@ -1653,25 +1653,25 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>1a8e1c0e-1f96-4de2-a33d-c932e74f2314</v>
+        <v>a12f5acf-4754-479a-853c-15926c2dac92</v>
       </c>
       <c r="B49" t="str">
-        <v>Ritmos latinos y caribeños</v>
+        <v>Ladys Tango - Gabriela P.</v>
       </c>
       <c r="C49" t="str">
-        <v>Histórica - Ritmos latinos y caribeños - 2025 - $15.000</v>
+        <v>Histórica - Ladys Tango - Gabriela P. - 2025 - $20.000</v>
       </c>
       <c r="D49" t="str">
-        <v>15000.00</v>
+        <v>20000.00</v>
       </c>
       <c r="E49" t="str">
-        <v>2025-02-01</v>
+        <v>2025-07-01</v>
       </c>
       <c r="F49" t="str">
-        <v>2025-02-28</v>
+        <v>2025-07-31</v>
       </c>
       <c r="G49" t="str">
-        <v>2025-02 = $15000.00</v>
+        <v>2025-07 = $20000.00</v>
       </c>
       <c r="H49" t="str">
         <v/>
@@ -1679,25 +1679,25 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>1a8e1c0e-1f96-4de2-a33d-c932e74f2314</v>
+        <v>b96017bd-9ee1-4bde-ad35-ad961a78e5f5</v>
       </c>
       <c r="B50" t="str">
-        <v>Ritmos latinos y caribeños</v>
+        <v>Mambo en parejas</v>
       </c>
       <c r="C50" t="str">
-        <v>Histórica - Ritmos latinos y caribeños - 2025 - $20.000</v>
+        <v>Histórica - Mambo en parejas - 2026 - $15.000</v>
       </c>
       <c r="D50" t="str">
-        <v>20000.00</v>
+        <v>15000.00</v>
       </c>
       <c r="E50" t="str">
-        <v>2025-03-01</v>
+        <v>2026-02-01</v>
       </c>
       <c r="F50" t="str">
-        <v>2025-07-31</v>
+        <v>2026-02-28</v>
       </c>
       <c r="G50" t="str">
-        <v>2025-03 = $20000.00</v>
+        <v>2026-02 = $15000.00</v>
       </c>
       <c r="H50" t="str">
         <v/>
@@ -1705,51 +1705,51 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>71bc486f-8a3d-46bb-a102-838cfef0a1fc</v>
+        <v>b96017bd-9ee1-4bde-ad35-ad961a78e5f5</v>
       </c>
       <c r="B51" t="str">
-        <v>S.C Adultos (+18 años)</v>
+        <v>Mambo en parejas</v>
       </c>
       <c r="C51" t="str">
-        <v>Histórica - S.C Adultos (+18 años) - 2025 - $15.000</v>
+        <v>Histórica - Mambo en parejas - 2026 - $30.000</v>
       </c>
       <c r="D51" t="str">
-        <v>15000.00</v>
+        <v>30000.00</v>
       </c>
       <c r="E51" t="str">
-        <v>2025-02-01</v>
+        <v>2026-03-01</v>
       </c>
       <c r="F51" t="str">
-        <v>2025-02-28</v>
+        <v>2026-07-31</v>
       </c>
       <c r="G51" t="str">
-        <v>2025-02 = $15000.00</v>
+        <v>2026-03 = $30000.00 | 2026-05 = $30000.00</v>
       </c>
       <c r="H51" t="str">
-        <v/>
+        <v>2026-07 ($15000.00)</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>71bc486f-8a3d-46bb-a102-838cfef0a1fc</v>
+        <v>b96017bd-9ee1-4bde-ad35-ad961a78e5f5</v>
       </c>
       <c r="B52" t="str">
-        <v>S.C Adultos (+18 años)</v>
+        <v>Mambo en parejas</v>
       </c>
       <c r="C52" t="str">
-        <v>Histórica - S.C Adultos (+18 años) - 2025 - $20.000</v>
+        <v>Histórica - Mambo en parejas - 2026 - $40.000</v>
       </c>
       <c r="D52" t="str">
-        <v>20000.00</v>
+        <v>40000.00</v>
       </c>
       <c r="E52" t="str">
-        <v>2025-03-01</v>
+        <v>2026-08-01</v>
       </c>
       <c r="F52" t="str">
-        <v>2025-04-30</v>
+        <v>2026-08-31</v>
       </c>
       <c r="G52" t="str">
-        <v>2025-03 = $20000.00</v>
+        <v>2026-08 = $40000.00</v>
       </c>
       <c r="H52" t="str">
         <v/>
@@ -1757,13 +1757,13 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>4b2663bf-5ab4-42e5-865c-2af4da2cf5ff</v>
+        <v>1a8e1c0e-1f96-4de2-a33d-c932e74f2314</v>
       </c>
       <c r="B53" t="str">
-        <v>S.C Infantil (6-11 años)</v>
+        <v>Ritmos latinos y caribeños</v>
       </c>
       <c r="C53" t="str">
-        <v>Histórica - S.C Infantil (6-11 años) - 2025 - $15.000</v>
+        <v>Histórica - Ritmos latinos y caribeños - 2025 - $15.000</v>
       </c>
       <c r="D53" t="str">
         <v>15000.00</v>
@@ -1783,13 +1783,13 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>4b2663bf-5ab4-42e5-865c-2af4da2cf5ff</v>
+        <v>1a8e1c0e-1f96-4de2-a33d-c932e74f2314</v>
       </c>
       <c r="B54" t="str">
-        <v>S.C Infantil (6-11 años)</v>
+        <v>Ritmos latinos y caribeños</v>
       </c>
       <c r="C54" t="str">
-        <v>Histórica - S.C Infantil (6-11 años) - 2025 - $20.000</v>
+        <v>Histórica - Ritmos latinos y caribeños - 2025 - $20.000</v>
       </c>
       <c r="D54" t="str">
         <v>20000.00</v>
@@ -1798,7 +1798,7 @@
         <v>2025-03-01</v>
       </c>
       <c r="F54" t="str">
-        <v>2025-04-30</v>
+        <v>2025-07-31</v>
       </c>
       <c r="G54" t="str">
         <v>2025-03 = $20000.00</v>
@@ -1809,13 +1809,13 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>f8a32bf2-9e2a-48b5-9f2e-a8b9da860fb3</v>
+        <v>71bc486f-8a3d-46bb-a102-838cfef0a1fc</v>
       </c>
       <c r="B55" t="str">
-        <v>S.C Juvenil (12-17 años)</v>
+        <v>S.C Adultos (+18 años)</v>
       </c>
       <c r="C55" t="str">
-        <v>Histórica - S.C Juvenil (12-17 años) - 2025 - $15.000</v>
+        <v>Histórica - S.C Adultos (+18 años) - 2025 - $15.000</v>
       </c>
       <c r="D55" t="str">
         <v>15000.00</v>
@@ -1835,13 +1835,13 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>f8a32bf2-9e2a-48b5-9f2e-a8b9da860fb3</v>
+        <v>71bc486f-8a3d-46bb-a102-838cfef0a1fc</v>
       </c>
       <c r="B56" t="str">
-        <v>S.C Juvenil (12-17 años)</v>
+        <v>S.C Adultos (+18 años)</v>
       </c>
       <c r="C56" t="str">
-        <v>Histórica - S.C Juvenil (12-17 años) - 2025 - $20.000</v>
+        <v>Histórica - S.C Adultos (+18 años) - 2025 - $20.000</v>
       </c>
       <c r="D56" t="str">
         <v>20000.00</v>
@@ -1850,10 +1850,10 @@
         <v>2025-03-01</v>
       </c>
       <c r="F56" t="str">
-        <v>2025-04-30</v>
+        <v>2025-08-31</v>
       </c>
       <c r="G56" t="str">
-        <v>2025-03 = $20000.00</v>
+        <v>2025-03 = $20000.00 | 2025-05 = $20000.00</v>
       </c>
       <c r="H56" t="str">
         <v/>
@@ -1861,25 +1861,25 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>dd4b0323-e82f-4b02-89c0-0f8e520033ed</v>
+        <v>71bc486f-8a3d-46bb-a102-838cfef0a1fc</v>
       </c>
       <c r="B57" t="str">
-        <v>Street Int/Avanzado</v>
+        <v>S.C Adultos (+18 años)</v>
       </c>
       <c r="C57" t="str">
-        <v>Histórica - Street Int/Avanzado - 2025 - $15.000</v>
+        <v>Histórica - S.C Adultos (+18 años) - 2025 - $30.000</v>
       </c>
       <c r="D57" t="str">
-        <v>15000.00</v>
+        <v>30000.00</v>
       </c>
       <c r="E57" t="str">
-        <v>2025-02-01</v>
+        <v>2025-09-01</v>
       </c>
       <c r="F57" t="str">
-        <v>2025-02-28</v>
+        <v>2025-11-30</v>
       </c>
       <c r="G57" t="str">
-        <v>2025-02 = $15000.00</v>
+        <v>2025-09 = $30000.00</v>
       </c>
       <c r="H57" t="str">
         <v/>
@@ -1887,25 +1887,25 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>dd4b0323-e82f-4b02-89c0-0f8e520033ed</v>
+        <v>71bc486f-8a3d-46bb-a102-838cfef0a1fc</v>
       </c>
       <c r="B58" t="str">
-        <v>Street Int/Avanzado</v>
+        <v>S.C Adultos (+18 años)</v>
       </c>
       <c r="C58" t="str">
-        <v>Histórica - Street Int/Avanzado - 2025 - $20.000</v>
+        <v>Histórica - S.C Adultos (+18 años) - 2026 - $30.000</v>
       </c>
       <c r="D58" t="str">
-        <v>20000.00</v>
+        <v>30000.00</v>
       </c>
       <c r="E58" t="str">
-        <v>2025-03-01</v>
+        <v>2026-01-01</v>
       </c>
       <c r="F58" t="str">
-        <v>2025-04-30</v>
+        <v>2026-06-30</v>
       </c>
       <c r="G58" t="str">
-        <v>2025-03 = $20000.00</v>
+        <v>2026-01 = $30000.00</v>
       </c>
       <c r="H58" t="str">
         <v/>
@@ -1913,25 +1913,25 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>cc392129-75e3-4205-b7fc-fafceb55b996</v>
+        <v>71bc486f-8a3d-46bb-a102-838cfef0a1fc</v>
       </c>
       <c r="B59" t="str">
-        <v>Tango (Inter/Avanz)</v>
+        <v>S.C Adultos (+18 años)</v>
       </c>
       <c r="C59" t="str">
-        <v>Histórica - Tango (Inter/Avanz) - 2025 - $15.000</v>
+        <v>Histórica - S.C Adultos (+18 años) - 2026 - $15.000</v>
       </c>
       <c r="D59" t="str">
         <v>15000.00</v>
       </c>
       <c r="E59" t="str">
-        <v>2025-02-01</v>
+        <v>2026-07-01</v>
       </c>
       <c r="F59" t="str">
-        <v>2025-02-28</v>
+        <v>2026-07-31</v>
       </c>
       <c r="G59" t="str">
-        <v>2025-02 = $15000.00</v>
+        <v>2026-07 = $15000.00</v>
       </c>
       <c r="H59" t="str">
         <v/>
@@ -1939,25 +1939,25 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>cc392129-75e3-4205-b7fc-fafceb55b996</v>
+        <v>71bc486f-8a3d-46bb-a102-838cfef0a1fc</v>
       </c>
       <c r="B60" t="str">
-        <v>Tango (Inter/Avanz)</v>
+        <v>S.C Adultos (+18 años)</v>
       </c>
       <c r="C60" t="str">
-        <v>Histórica - Tango (Inter/Avanz) - 2025 - $20.000</v>
+        <v>Histórica - S.C Adultos (+18 años) - 2026 - $40.000</v>
       </c>
       <c r="D60" t="str">
-        <v>20000.00</v>
+        <v>40000.00</v>
       </c>
       <c r="E60" t="str">
-        <v>2025-03-01</v>
+        <v>2026-08-01</v>
       </c>
       <c r="F60" t="str">
-        <v>2025-08-31</v>
+        <v>2026-08-31</v>
       </c>
       <c r="G60" t="str">
-        <v>2025-03 = $20000.00</v>
+        <v>2026-08 = $40000.00</v>
       </c>
       <c r="H60" t="str">
         <v/>
@@ -1965,25 +1965,25 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>cc392129-75e3-4205-b7fc-fafceb55b996</v>
+        <v>4b2663bf-5ab4-42e5-865c-2af4da2cf5ff</v>
       </c>
       <c r="B61" t="str">
-        <v>Tango (Inter/Avanz)</v>
+        <v>S.C Infantil (6-11 años)</v>
       </c>
       <c r="C61" t="str">
-        <v>Histórica - Tango (Inter/Avanz) - 2025 - $30.000</v>
+        <v>Histórica - S.C Infantil (6-11 años) - 2025 - $15.000</v>
       </c>
       <c r="D61" t="str">
-        <v>30000.00</v>
+        <v>15000.00</v>
       </c>
       <c r="E61" t="str">
-        <v>2025-09-01</v>
+        <v>2025-02-01</v>
       </c>
       <c r="F61" t="str">
-        <v>2025-11-30</v>
+        <v>2025-02-28</v>
       </c>
       <c r="G61" t="str">
-        <v>2025-09 = $30000.00</v>
+        <v>2025-02 = $15000.00</v>
       </c>
       <c r="H61" t="str">
         <v/>
@@ -1991,51 +1991,51 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>cc392129-75e3-4205-b7fc-fafceb55b996</v>
+        <v>4b2663bf-5ab4-42e5-865c-2af4da2cf5ff</v>
       </c>
       <c r="B62" t="str">
-        <v>Tango (Inter/Avanz)</v>
+        <v>S.C Infantil (6-11 años)</v>
       </c>
       <c r="C62" t="str">
-        <v>Histórica - Tango (Inter/Avanz) - 2026 - $30.000</v>
+        <v>Histórica - S.C Infantil (6-11 años) - 2025 - $20.000</v>
       </c>
       <c r="D62" t="str">
-        <v>30000.00</v>
+        <v>20000.00</v>
       </c>
       <c r="E62" t="str">
-        <v>2026-03-01</v>
+        <v>2025-03-01</v>
       </c>
       <c r="F62" t="str">
-        <v>2026-07-31</v>
+        <v>2025-08-31</v>
       </c>
       <c r="G62" t="str">
-        <v>2026-03 = $30000.00 | 2026-05 = $30000.00</v>
+        <v>2025-03 = $20000.00 | 2025-05 = $20000.00</v>
       </c>
       <c r="H62" t="str">
-        <v>2026-07 ($15000.00)</v>
+        <v/>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>cc392129-75e3-4205-b7fc-fafceb55b996</v>
+        <v>4b2663bf-5ab4-42e5-865c-2af4da2cf5ff</v>
       </c>
       <c r="B63" t="str">
-        <v>Tango (Inter/Avanz)</v>
+        <v>S.C Infantil (6-11 años)</v>
       </c>
       <c r="C63" t="str">
-        <v>Histórica - Tango (Inter/Avanz) - 2026 - $40.000</v>
+        <v>Histórica - S.C Infantil (6-11 años) - 2025 - $30.000</v>
       </c>
       <c r="D63" t="str">
-        <v>40000.00</v>
+        <v>30000.00</v>
       </c>
       <c r="E63" t="str">
-        <v>2026-08-01</v>
+        <v>2025-09-01</v>
       </c>
       <c r="F63" t="str">
-        <v>2026-08-31</v>
+        <v>2025-11-30</v>
       </c>
       <c r="G63" t="str">
-        <v>2026-08 = $40000.00</v>
+        <v>2025-09 = $30000.00</v>
       </c>
       <c r="H63" t="str">
         <v/>
@@ -2043,25 +2043,25 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>23888530-c53d-4c40-94ee-982518e5d2f6</v>
+        <v>4b2663bf-5ab4-42e5-865c-2af4da2cf5ff</v>
       </c>
       <c r="B64" t="str">
-        <v>Tango Inicial</v>
+        <v>S.C Infantil (6-11 años)</v>
       </c>
       <c r="C64" t="str">
-        <v>Histórica - Tango Inicial - 2026 - $30.000</v>
+        <v>Histórica - S.C Infantil (6-11 años) - 2026 - $30.000</v>
       </c>
       <c r="D64" t="str">
         <v>30000.00</v>
       </c>
       <c r="E64" t="str">
-        <v>2026-03-01</v>
+        <v>2026-01-01</v>
       </c>
       <c r="F64" t="str">
-        <v>2026-03-31</v>
+        <v>2026-06-30</v>
       </c>
       <c r="G64" t="str">
-        <v>2026-03 = $30000.00</v>
+        <v>2026-01 = $30000.00</v>
       </c>
       <c r="H64" t="str">
         <v/>
@@ -2069,25 +2069,25 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>da4d15d9-c846-4098-8640-e95fd97c604f</v>
+        <v>4b2663bf-5ab4-42e5-865c-2af4da2cf5ff</v>
       </c>
       <c r="B65" t="str">
-        <v>Teens (8 a 12 años)</v>
+        <v>S.C Infantil (6-11 años)</v>
       </c>
       <c r="C65" t="str">
-        <v>Histórica - Teens (8 a 12 años) - 2025 - $15.000</v>
+        <v>Histórica - S.C Infantil (6-11 años) - 2026 - $15.000</v>
       </c>
       <c r="D65" t="str">
         <v>15000.00</v>
       </c>
       <c r="E65" t="str">
-        <v>2025-02-01</v>
+        <v>2026-07-01</v>
       </c>
       <c r="F65" t="str">
-        <v>2025-02-28</v>
+        <v>2026-07-31</v>
       </c>
       <c r="G65" t="str">
-        <v>2025-02 = $15000.00</v>
+        <v>2026-07 = $15000.00</v>
       </c>
       <c r="H65" t="str">
         <v/>
@@ -2095,25 +2095,25 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>da4d15d9-c846-4098-8640-e95fd97c604f</v>
+        <v>4b2663bf-5ab4-42e5-865c-2af4da2cf5ff</v>
       </c>
       <c r="B66" t="str">
-        <v>Teens (8 a 12 años)</v>
+        <v>S.C Infantil (6-11 años)</v>
       </c>
       <c r="C66" t="str">
-        <v>Histórica - Teens (8 a 12 años) - 2025 - $20.000</v>
+        <v>Histórica - S.C Infantil (6-11 años) - 2026 - $40.000</v>
       </c>
       <c r="D66" t="str">
-        <v>20000.00</v>
+        <v>40000.00</v>
       </c>
       <c r="E66" t="str">
-        <v>2025-03-01</v>
+        <v>2026-08-01</v>
       </c>
       <c r="F66" t="str">
-        <v>2025-08-31</v>
+        <v>2026-08-31</v>
       </c>
       <c r="G66" t="str">
-        <v>2025-03 = $20000.00</v>
+        <v>2026-08 = $40000.00</v>
       </c>
       <c r="H66" t="str">
         <v/>
@@ -2121,25 +2121,25 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>da4d15d9-c846-4098-8640-e95fd97c604f</v>
+        <v>f8a32bf2-9e2a-48b5-9f2e-a8b9da860fb3</v>
       </c>
       <c r="B67" t="str">
-        <v>Teens (8 a 12 años)</v>
+        <v>S.C Juvenil (12-17 años)</v>
       </c>
       <c r="C67" t="str">
-        <v>Histórica - Teens (8 a 12 años) - 2025 - $30.000</v>
+        <v>Histórica - S.C Juvenil (12-17 años) - 2025 - $15.000</v>
       </c>
       <c r="D67" t="str">
-        <v>30000.00</v>
+        <v>15000.00</v>
       </c>
       <c r="E67" t="str">
-        <v>2025-09-01</v>
+        <v>2025-02-01</v>
       </c>
       <c r="F67" t="str">
-        <v>2025-10-31</v>
+        <v>2025-02-28</v>
       </c>
       <c r="G67" t="str">
-        <v>2025-09 = $30000.00</v>
+        <v>2025-02 = $15000.00</v>
       </c>
       <c r="H67" t="str">
         <v/>
@@ -2147,25 +2147,25 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>da4d15d9-c846-4098-8640-e95fd97c604f</v>
+        <v>f8a32bf2-9e2a-48b5-9f2e-a8b9da860fb3</v>
       </c>
       <c r="B68" t="str">
-        <v>Teens (8 a 12 años)</v>
+        <v>S.C Juvenil (12-17 años)</v>
       </c>
       <c r="C68" t="str">
-        <v>Histórica - Teens (8 a 12 años) - 2025 - $25.000</v>
+        <v>Histórica - S.C Juvenil (12-17 años) - 2025 - $20.000</v>
       </c>
       <c r="D68" t="str">
-        <v>25000.00</v>
+        <v>20000.00</v>
       </c>
       <c r="E68" t="str">
-        <v>2025-11-01</v>
+        <v>2025-03-01</v>
       </c>
       <c r="F68" t="str">
-        <v>2025-11-30</v>
+        <v>2025-08-31</v>
       </c>
       <c r="G68" t="str">
-        <v>2025-11 = $25000.00</v>
+        <v>2025-03 = $20000.00 | 2025-05 = $20000.00</v>
       </c>
       <c r="H68" t="str">
         <v/>
@@ -2173,25 +2173,25 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>da4d15d9-c846-4098-8640-e95fd97c604f</v>
+        <v>f8a32bf2-9e2a-48b5-9f2e-a8b9da860fb3</v>
       </c>
       <c r="B69" t="str">
-        <v>Teens (8 a 12 años)</v>
+        <v>S.C Juvenil (12-17 años)</v>
       </c>
       <c r="C69" t="str">
-        <v>Histórica - Teens (8 a 12 años) - 2026 - $30.000</v>
+        <v>Histórica - S.C Juvenil (12-17 años) - 2025 - $30.000</v>
       </c>
       <c r="D69" t="str">
         <v>30000.00</v>
       </c>
       <c r="E69" t="str">
-        <v>2026-01-01</v>
+        <v>2025-09-01</v>
       </c>
       <c r="F69" t="str">
-        <v>2026-01-31</v>
+        <v>2025-11-30</v>
       </c>
       <c r="G69" t="str">
-        <v>2026-01 = $30000.00</v>
+        <v>2025-09 = $30000.00</v>
       </c>
       <c r="H69" t="str">
         <v/>
@@ -2199,25 +2199,25 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>da4d15d9-c846-4098-8640-e95fd97c604f</v>
+        <v>f8a32bf2-9e2a-48b5-9f2e-a8b9da860fb3</v>
       </c>
       <c r="B70" t="str">
-        <v>Teens (8 a 12 años)</v>
+        <v>S.C Juvenil (12-17 años)</v>
       </c>
       <c r="C70" t="str">
-        <v>Histórica - Teens (8 a 12 años) - 2026 - $15.000</v>
+        <v>Histórica - S.C Juvenil (12-17 años) - 2026 - $30.000</v>
       </c>
       <c r="D70" t="str">
-        <v>15000.00</v>
+        <v>30000.00</v>
       </c>
       <c r="E70" t="str">
-        <v>2026-02-01</v>
+        <v>2026-01-01</v>
       </c>
       <c r="F70" t="str">
-        <v>2026-02-28</v>
+        <v>2026-06-30</v>
       </c>
       <c r="G70" t="str">
-        <v>2026-02 = $15000.00</v>
+        <v>2026-01 = $30000.00</v>
       </c>
       <c r="H70" t="str">
         <v/>
@@ -2225,39 +2225,39 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>da4d15d9-c846-4098-8640-e95fd97c604f</v>
+        <v>f8a32bf2-9e2a-48b5-9f2e-a8b9da860fb3</v>
       </c>
       <c r="B71" t="str">
-        <v>Teens (8 a 12 años)</v>
+        <v>S.C Juvenil (12-17 años)</v>
       </c>
       <c r="C71" t="str">
-        <v>Histórica - Teens (8 a 12 años) - 2026 - $30.000</v>
+        <v>Histórica - S.C Juvenil (12-17 años) - 2026 - $15.000</v>
       </c>
       <c r="D71" t="str">
-        <v>30000.00</v>
+        <v>15000.00</v>
       </c>
       <c r="E71" t="str">
-        <v>2026-03-01</v>
+        <v>2026-07-01</v>
       </c>
       <c r="F71" t="str">
         <v>2026-07-31</v>
       </c>
       <c r="G71" t="str">
-        <v>2026-03 = $30000.00 | 2026-05 = $30000.00</v>
+        <v>2026-07 = $15000.00</v>
       </c>
       <c r="H71" t="str">
-        <v>2026-07 ($15000.00)</v>
+        <v/>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>da4d15d9-c846-4098-8640-e95fd97c604f</v>
+        <v>f8a32bf2-9e2a-48b5-9f2e-a8b9da860fb3</v>
       </c>
       <c r="B72" t="str">
-        <v>Teens (8 a 12 años)</v>
+        <v>S.C Juvenil (12-17 años)</v>
       </c>
       <c r="C72" t="str">
-        <v>Histórica - Teens (8 a 12 años) - 2026 - $40.000</v>
+        <v>Histórica - S.C Juvenil (12-17 años) - 2026 - $40.000</v>
       </c>
       <c r="D72" t="str">
         <v>40000.00</v>
@@ -2277,59 +2277,579 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>5e8e8fd7-a08b-4443-8ba0-30ee263ffa1b</v>
+        <v>dd4b0323-e82f-4b02-89c0-0f8e520033ed</v>
       </c>
       <c r="B73" t="str">
-        <v>Zumba - Profe Joselo</v>
+        <v>Street Int/Avanzado</v>
       </c>
       <c r="C73" t="str">
-        <v>Histórica - Zumba - Profe Joselo - 2026 - $30.000</v>
+        <v>Histórica - Street Int/Avanzado - 2025 - $15.000</v>
       </c>
       <c r="D73" t="str">
-        <v>30000.00</v>
+        <v>15000.00</v>
       </c>
       <c r="E73" t="str">
-        <v>2026-05-01</v>
+        <v>2025-02-01</v>
       </c>
       <c r="F73" t="str">
-        <v>2026-07-31</v>
+        <v>2025-02-28</v>
       </c>
       <c r="G73" t="str">
-        <v>2026-05 = $30000.00</v>
+        <v>2025-02 = $15000.00</v>
       </c>
       <c r="H73" t="str">
-        <v>2026-07 ($15000.00)</v>
+        <v/>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
+        <v>dd4b0323-e82f-4b02-89c0-0f8e520033ed</v>
+      </c>
+      <c r="B74" t="str">
+        <v>Street Int/Avanzado</v>
+      </c>
+      <c r="C74" t="str">
+        <v>Histórica - Street Int/Avanzado - 2025 - $20.000</v>
+      </c>
+      <c r="D74" t="str">
+        <v>20000.00</v>
+      </c>
+      <c r="E74" t="str">
+        <v>2025-03-01</v>
+      </c>
+      <c r="F74" t="str">
+        <v>2025-08-31</v>
+      </c>
+      <c r="G74" t="str">
+        <v>2025-03 = $20000.00 | 2025-05 = $20000.00</v>
+      </c>
+      <c r="H74" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>dd4b0323-e82f-4b02-89c0-0f8e520033ed</v>
+      </c>
+      <c r="B75" t="str">
+        <v>Street Int/Avanzado</v>
+      </c>
+      <c r="C75" t="str">
+        <v>Histórica - Street Int/Avanzado - 2025 - $30.000</v>
+      </c>
+      <c r="D75" t="str">
+        <v>30000.00</v>
+      </c>
+      <c r="E75" t="str">
+        <v>2025-09-01</v>
+      </c>
+      <c r="F75" t="str">
+        <v>2025-11-30</v>
+      </c>
+      <c r="G75" t="str">
+        <v>2025-09 = $30000.00</v>
+      </c>
+      <c r="H75" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>dd4b0323-e82f-4b02-89c0-0f8e520033ed</v>
+      </c>
+      <c r="B76" t="str">
+        <v>Street Int/Avanzado</v>
+      </c>
+      <c r="C76" t="str">
+        <v>Histórica - Street Int/Avanzado - 2026 - $30.000</v>
+      </c>
+      <c r="D76" t="str">
+        <v>30000.00</v>
+      </c>
+      <c r="E76" t="str">
+        <v>2026-01-01</v>
+      </c>
+      <c r="F76" t="str">
+        <v>2026-06-30</v>
+      </c>
+      <c r="G76" t="str">
+        <v>2026-01 = $30000.00</v>
+      </c>
+      <c r="H76" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>dd4b0323-e82f-4b02-89c0-0f8e520033ed</v>
+      </c>
+      <c r="B77" t="str">
+        <v>Street Int/Avanzado</v>
+      </c>
+      <c r="C77" t="str">
+        <v>Histórica - Street Int/Avanzado - 2026 - $15.000</v>
+      </c>
+      <c r="D77" t="str">
+        <v>15000.00</v>
+      </c>
+      <c r="E77" t="str">
+        <v>2026-07-01</v>
+      </c>
+      <c r="F77" t="str">
+        <v>2026-07-31</v>
+      </c>
+      <c r="G77" t="str">
+        <v>2026-07 = $15000.00</v>
+      </c>
+      <c r="H77" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>dd4b0323-e82f-4b02-89c0-0f8e520033ed</v>
+      </c>
+      <c r="B78" t="str">
+        <v>Street Int/Avanzado</v>
+      </c>
+      <c r="C78" t="str">
+        <v>Histórica - Street Int/Avanzado - 2026 - $40.000</v>
+      </c>
+      <c r="D78" t="str">
+        <v>40000.00</v>
+      </c>
+      <c r="E78" t="str">
+        <v>2026-08-01</v>
+      </c>
+      <c r="F78" t="str">
+        <v>2026-08-31</v>
+      </c>
+      <c r="G78" t="str">
+        <v>2026-08 = $40000.00</v>
+      </c>
+      <c r="H78" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>cc392129-75e3-4205-b7fc-fafceb55b996</v>
+      </c>
+      <c r="B79" t="str">
+        <v>Tango (Inter/Avanz)</v>
+      </c>
+      <c r="C79" t="str">
+        <v>Histórica - Tango (Inter/Avanz) - 2025 - $15.000</v>
+      </c>
+      <c r="D79" t="str">
+        <v>15000.00</v>
+      </c>
+      <c r="E79" t="str">
+        <v>2025-02-01</v>
+      </c>
+      <c r="F79" t="str">
+        <v>2025-02-28</v>
+      </c>
+      <c r="G79" t="str">
+        <v>2025-02 = $15000.00</v>
+      </c>
+      <c r="H79" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>cc392129-75e3-4205-b7fc-fafceb55b996</v>
+      </c>
+      <c r="B80" t="str">
+        <v>Tango (Inter/Avanz)</v>
+      </c>
+      <c r="C80" t="str">
+        <v>Histórica - Tango (Inter/Avanz) - 2025 - $20.000</v>
+      </c>
+      <c r="D80" t="str">
+        <v>20000.00</v>
+      </c>
+      <c r="E80" t="str">
+        <v>2025-03-01</v>
+      </c>
+      <c r="F80" t="str">
+        <v>2025-08-31</v>
+      </c>
+      <c r="G80" t="str">
+        <v>2025-03 = $20000.00</v>
+      </c>
+      <c r="H80" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v>cc392129-75e3-4205-b7fc-fafceb55b996</v>
+      </c>
+      <c r="B81" t="str">
+        <v>Tango (Inter/Avanz)</v>
+      </c>
+      <c r="C81" t="str">
+        <v>Histórica - Tango (Inter/Avanz) - 2025 - $30.000</v>
+      </c>
+      <c r="D81" t="str">
+        <v>30000.00</v>
+      </c>
+      <c r="E81" t="str">
+        <v>2025-09-01</v>
+      </c>
+      <c r="F81" t="str">
+        <v>2025-11-30</v>
+      </c>
+      <c r="G81" t="str">
+        <v>2025-09 = $30000.00</v>
+      </c>
+      <c r="H81" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>cc392129-75e3-4205-b7fc-fafceb55b996</v>
+      </c>
+      <c r="B82" t="str">
+        <v>Tango (Inter/Avanz)</v>
+      </c>
+      <c r="C82" t="str">
+        <v>Histórica - Tango (Inter/Avanz) - 2026 - $30.000</v>
+      </c>
+      <c r="D82" t="str">
+        <v>30000.00</v>
+      </c>
+      <c r="E82" t="str">
+        <v>2026-03-01</v>
+      </c>
+      <c r="F82" t="str">
+        <v>2026-07-31</v>
+      </c>
+      <c r="G82" t="str">
+        <v>2026-03 = $30000.00 | 2026-05 = $30000.00</v>
+      </c>
+      <c r="H82" t="str">
+        <v>2026-07 ($15000.00)</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>cc392129-75e3-4205-b7fc-fafceb55b996</v>
+      </c>
+      <c r="B83" t="str">
+        <v>Tango (Inter/Avanz)</v>
+      </c>
+      <c r="C83" t="str">
+        <v>Histórica - Tango (Inter/Avanz) - 2026 - $40.000</v>
+      </c>
+      <c r="D83" t="str">
+        <v>40000.00</v>
+      </c>
+      <c r="E83" t="str">
+        <v>2026-08-01</v>
+      </c>
+      <c r="F83" t="str">
+        <v>2026-08-31</v>
+      </c>
+      <c r="G83" t="str">
+        <v>2026-08 = $40000.00</v>
+      </c>
+      <c r="H83" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>23888530-c53d-4c40-94ee-982518e5d2f6</v>
+      </c>
+      <c r="B84" t="str">
+        <v>Tango Inicial</v>
+      </c>
+      <c r="C84" t="str">
+        <v>Histórica - Tango Inicial - 2026 - $30.000</v>
+      </c>
+      <c r="D84" t="str">
+        <v>30000.00</v>
+      </c>
+      <c r="E84" t="str">
+        <v>2026-03-01</v>
+      </c>
+      <c r="F84" t="str">
+        <v>2026-03-31</v>
+      </c>
+      <c r="G84" t="str">
+        <v>2026-03 = $30000.00</v>
+      </c>
+      <c r="H84" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>da4d15d9-c846-4098-8640-e95fd97c604f</v>
+      </c>
+      <c r="B85" t="str">
+        <v>Teens (8 a 12 años)</v>
+      </c>
+      <c r="C85" t="str">
+        <v>Histórica - Teens (8 a 12 años) - 2025 - $15.000</v>
+      </c>
+      <c r="D85" t="str">
+        <v>15000.00</v>
+      </c>
+      <c r="E85" t="str">
+        <v>2025-02-01</v>
+      </c>
+      <c r="F85" t="str">
+        <v>2025-02-28</v>
+      </c>
+      <c r="G85" t="str">
+        <v>2025-02 = $15000.00</v>
+      </c>
+      <c r="H85" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>da4d15d9-c846-4098-8640-e95fd97c604f</v>
+      </c>
+      <c r="B86" t="str">
+        <v>Teens (8 a 12 años)</v>
+      </c>
+      <c r="C86" t="str">
+        <v>Histórica - Teens (8 a 12 años) - 2025 - $20.000</v>
+      </c>
+      <c r="D86" t="str">
+        <v>20000.00</v>
+      </c>
+      <c r="E86" t="str">
+        <v>2025-03-01</v>
+      </c>
+      <c r="F86" t="str">
+        <v>2025-08-31</v>
+      </c>
+      <c r="G86" t="str">
+        <v>2025-03 = $20000.00</v>
+      </c>
+      <c r="H86" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v>da4d15d9-c846-4098-8640-e95fd97c604f</v>
+      </c>
+      <c r="B87" t="str">
+        <v>Teens (8 a 12 años)</v>
+      </c>
+      <c r="C87" t="str">
+        <v>Histórica - Teens (8 a 12 años) - 2025 - $30.000</v>
+      </c>
+      <c r="D87" t="str">
+        <v>30000.00</v>
+      </c>
+      <c r="E87" t="str">
+        <v>2025-09-01</v>
+      </c>
+      <c r="F87" t="str">
+        <v>2025-10-31</v>
+      </c>
+      <c r="G87" t="str">
+        <v>2025-09 = $30000.00</v>
+      </c>
+      <c r="H87" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>da4d15d9-c846-4098-8640-e95fd97c604f</v>
+      </c>
+      <c r="B88" t="str">
+        <v>Teens (8 a 12 años)</v>
+      </c>
+      <c r="C88" t="str">
+        <v>Histórica - Teens (8 a 12 años) - 2025 - $25.000</v>
+      </c>
+      <c r="D88" t="str">
+        <v>25000.00</v>
+      </c>
+      <c r="E88" t="str">
+        <v>2025-11-01</v>
+      </c>
+      <c r="F88" t="str">
+        <v>2025-11-30</v>
+      </c>
+      <c r="G88" t="str">
+        <v>2025-11 = $25000.00</v>
+      </c>
+      <c r="H88" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>da4d15d9-c846-4098-8640-e95fd97c604f</v>
+      </c>
+      <c r="B89" t="str">
+        <v>Teens (8 a 12 años)</v>
+      </c>
+      <c r="C89" t="str">
+        <v>Histórica - Teens (8 a 12 años) - 2026 - $30.000</v>
+      </c>
+      <c r="D89" t="str">
+        <v>30000.00</v>
+      </c>
+      <c r="E89" t="str">
+        <v>2026-01-01</v>
+      </c>
+      <c r="F89" t="str">
+        <v>2026-01-31</v>
+      </c>
+      <c r="G89" t="str">
+        <v>2026-01 = $30000.00</v>
+      </c>
+      <c r="H89" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>da4d15d9-c846-4098-8640-e95fd97c604f</v>
+      </c>
+      <c r="B90" t="str">
+        <v>Teens (8 a 12 años)</v>
+      </c>
+      <c r="C90" t="str">
+        <v>Histórica - Teens (8 a 12 años) - 2026 - $15.000</v>
+      </c>
+      <c r="D90" t="str">
+        <v>15000.00</v>
+      </c>
+      <c r="E90" t="str">
+        <v>2026-02-01</v>
+      </c>
+      <c r="F90" t="str">
+        <v>2026-02-28</v>
+      </c>
+      <c r="G90" t="str">
+        <v>2026-02 = $15000.00</v>
+      </c>
+      <c r="H90" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>da4d15d9-c846-4098-8640-e95fd97c604f</v>
+      </c>
+      <c r="B91" t="str">
+        <v>Teens (8 a 12 años)</v>
+      </c>
+      <c r="C91" t="str">
+        <v>Histórica - Teens (8 a 12 años) - 2026 - $30.000</v>
+      </c>
+      <c r="D91" t="str">
+        <v>30000.00</v>
+      </c>
+      <c r="E91" t="str">
+        <v>2026-03-01</v>
+      </c>
+      <c r="F91" t="str">
+        <v>2026-07-31</v>
+      </c>
+      <c r="G91" t="str">
+        <v>2026-03 = $30000.00 | 2026-05 = $30000.00</v>
+      </c>
+      <c r="H91" t="str">
+        <v>2026-07 ($15000.00)</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v>da4d15d9-c846-4098-8640-e95fd97c604f</v>
+      </c>
+      <c r="B92" t="str">
+        <v>Teens (8 a 12 años)</v>
+      </c>
+      <c r="C92" t="str">
+        <v>Histórica - Teens (8 a 12 años) - 2026 - $40.000</v>
+      </c>
+      <c r="D92" t="str">
+        <v>40000.00</v>
+      </c>
+      <c r="E92" t="str">
+        <v>2026-08-01</v>
+      </c>
+      <c r="F92" t="str">
+        <v>2026-08-31</v>
+      </c>
+      <c r="G92" t="str">
+        <v>2026-08 = $40000.00</v>
+      </c>
+      <c r="H92" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
         <v>5e8e8fd7-a08b-4443-8ba0-30ee263ffa1b</v>
       </c>
-      <c r="B74" t="str">
+      <c r="B93" t="str">
         <v>Zumba - Profe Joselo</v>
       </c>
-      <c r="C74" t="str">
+      <c r="C93" t="str">
+        <v>Histórica - Zumba - Profe Joselo - 2026 - $30.000</v>
+      </c>
+      <c r="D93" t="str">
+        <v>30000.00</v>
+      </c>
+      <c r="E93" t="str">
+        <v>2026-05-01</v>
+      </c>
+      <c r="F93" t="str">
+        <v>2026-07-31</v>
+      </c>
+      <c r="G93" t="str">
+        <v>2026-05 = $30000.00</v>
+      </c>
+      <c r="H93" t="str">
+        <v>2026-07 ($15000.00)</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v>5e8e8fd7-a08b-4443-8ba0-30ee263ffa1b</v>
+      </c>
+      <c r="B94" t="str">
+        <v>Zumba - Profe Joselo</v>
+      </c>
+      <c r="C94" t="str">
         <v>Histórica - Zumba - Profe Joselo - 2026 - $40.000</v>
       </c>
-      <c r="D74" t="str">
+      <c r="D94" t="str">
         <v>40000.00</v>
       </c>
-      <c r="E74" t="str">
+      <c r="E94" t="str">
         <v>2026-08-01</v>
       </c>
-      <c r="F74" t="str">
+      <c r="F94" t="str">
         <v>2026-08-31</v>
       </c>
-      <c r="G74" t="str">
+      <c r="G94" t="str">
         <v>2026-08 = $40000.00</v>
       </c>
-      <c r="H74" t="str">
+      <c r="H94" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H74"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H94"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2727,7 +3247,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B10"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2774,7 +3294,7 @@
         <v>Tarifas consolidadas</v>
       </c>
       <c r="B6">
-        <v>73</v>
+        <v>93</v>
       </c>
     </row>
     <row r="7">
@@ -2801,9 +3321,17 @@
         <v>0</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Períodos confirmados por PO</v>
+      </c>
+      <c r="B10">
+        <v>25</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B10"/>
   </ignoredErrors>
 </worksheet>
 </file>